--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="162">
   <si>
     <t>Materia</t>
   </si>
@@ -993,7 +993,7 @@
         <v>-1</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>8</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1070,7 +1070,7 @@
         <v>-1</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>8</v>
@@ -1124,7 +1124,7 @@
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1147,7 +1147,7 @@
         <v>-1</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -1201,7 +1201,7 @@
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>-1</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>9</v>
@@ -1278,7 +1278,7 @@
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1301,7 +1301,7 @@
         <v>-1</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -1355,7 +1355,7 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1378,7 +1378,7 @@
         <v>-1</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1432,7 +1432,7 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1455,7 +1455,7 @@
         <v>-1</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1509,7 +1509,7 @@
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -1532,7 +1532,7 @@
         <v>-1</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1586,7 +1586,7 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1609,7 +1609,7 @@
         <v>-1</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -1663,7 +1663,7 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1686,7 +1686,7 @@
         <v>-1</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>10</v>
@@ -1740,7 +1740,7 @@
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1763,7 +1763,7 @@
         <v>-1</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D14">
         <v>10</v>
@@ -1817,7 +1817,7 @@
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1840,7 +1840,7 @@
         <v>-1</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>6</v>
@@ -1894,7 +1894,7 @@
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1917,7 +1917,7 @@
         <v>-1</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>9</v>
@@ -1971,7 +1971,7 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1994,7 +1994,7 @@
         <v>-1</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>6</v>
@@ -2048,7 +2048,7 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>6</v>
@@ -2071,7 +2071,7 @@
         <v>-1</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -2125,7 +2125,7 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2148,7 +2148,7 @@
         <v>-1</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2202,7 +2202,7 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2225,7 +2225,7 @@
         <v>-1</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>10</v>
@@ -2279,7 +2279,7 @@
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2302,7 +2302,7 @@
         <v>-1</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>5</v>
@@ -2356,7 +2356,7 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2379,7 +2379,7 @@
         <v>-1</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2433,7 +2433,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2456,7 +2456,7 @@
         <v>-1</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -2510,7 +2510,7 @@
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2533,7 +2533,7 @@
         <v>-1</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -2587,7 +2587,7 @@
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2610,7 +2610,7 @@
         <v>-1</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D25">
         <v>10</v>
@@ -2664,7 +2664,7 @@
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2687,7 +2687,7 @@
         <v>-1</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>10</v>
@@ -2741,7 +2741,7 @@
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2764,7 +2764,7 @@
         <v>-1</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -2818,7 +2818,7 @@
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -2841,7 +2841,7 @@
         <v>-1</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>9</v>
@@ -2895,7 +2895,7 @@
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -2918,7 +2918,7 @@
         <v>-1</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>9</v>
@@ -2972,7 +2972,7 @@
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2995,7 +2995,7 @@
         <v>-1</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -3049,7 +3049,7 @@
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -3072,7 +3072,7 @@
         <v>-1</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -3126,7 +3126,7 @@
         <v>-1</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -3149,7 +3149,7 @@
         <v>-1</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>10</v>
@@ -3203,7 +3203,7 @@
         <v>-1</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>10</v>
@@ -3226,7 +3226,7 @@
         <v>-1</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>10</v>
@@ -3280,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>10</v>
@@ -3303,7 +3303,7 @@
         <v>-1</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -3357,7 +3357,7 @@
         <v>-1</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3380,7 +3380,7 @@
         <v>-1</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D35">
         <v>10</v>
@@ -3434,7 +3434,7 @@
         <v>-1</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>-1</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>6</v>
@@ -3511,7 +3511,7 @@
         <v>-1</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -3534,7 +3534,7 @@
         <v>-1</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>8</v>
@@ -3588,7 +3588,7 @@
         <v>-1</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3611,7 +3611,7 @@
         <v>-1</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -3665,7 +3665,7 @@
         <v>-1</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
         <v>10</v>
@@ -3688,7 +3688,7 @@
         <v>-1</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>9</v>
@@ -3742,7 +3742,7 @@
         <v>-1</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V39">
         <v>9</v>
@@ -3765,7 +3765,7 @@
         <v>-1</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>6</v>
@@ -3819,7 +3819,7 @@
         <v>-1</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V40">
         <v>6</v>
@@ -3842,7 +3842,7 @@
         <v>-1</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -3896,7 +3896,7 @@
         <v>-1</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V41">
         <v>6</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>90</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D5">
         <v>90</v>
@@ -4147,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>90</v>
@@ -4206,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D7">
         <v>95</v>
@@ -4265,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -4324,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D9">
         <v>95</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -4442,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D11">
         <v>95</v>
@@ -4501,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D12">
         <v>100</v>
@@ -4560,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>95</v>
@@ -4619,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D14">
         <v>95</v>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D15">
         <v>90</v>
@@ -4737,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>95</v>
@@ -4796,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D17">
         <v>90</v>
@@ -4855,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D18">
         <v>80</v>
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D19">
         <v>95</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>100</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D21">
         <v>80</v>
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>100</v>
@@ -5150,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D23">
         <v>80</v>
@@ -5209,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D24">
         <v>90</v>
@@ -5268,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>100</v>
@@ -5327,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>100</v>
@@ -5386,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -5445,7 +5445,7 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>90</v>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>100</v>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D30">
         <v>85</v>
@@ -5622,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -5740,7 +5740,7 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D33">
         <v>95</v>
@@ -5799,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>85</v>
@@ -5858,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -5917,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D36">
         <v>90</v>
@@ -5976,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D37">
         <v>90</v>
@@ -6035,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>100</v>
@@ -6153,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D40">
         <v>95</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D41">
         <v>95</v>
@@ -6344,7 +6344,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -6373,7 +6373,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -6382,27 +6382,30 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>26.32</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
       <c r="I4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6411,19 +6414,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="G5">
-        <v>26.32</v>
+        <v>21.05</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6434,7 +6437,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -6443,19 +6446,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>78.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G6">
-        <v>21.05</v>
+        <v>15.79</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6466,7 +6469,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -6475,19 +6478,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>84.20999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="G7">
-        <v>15.79</v>
+        <v>7.89</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6503,7 +6506,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6564,7 +6567,7 @@
         <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>62</v>
@@ -6572,19 +6575,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920215</v>
+        <v>21330051920216</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
@@ -6604,7 +6607,7 @@
         <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>62</v>
@@ -6612,19 +6615,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920216</v>
+        <v>21330051920033</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
@@ -6632,16 +6635,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920216</v>
+        <v>21330051920033</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -6652,16 +6655,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920033</v>
+        <v>21330051920217</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -6672,19 +6675,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920033</v>
+        <v>21330051920217</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
@@ -6692,19 +6695,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920033</v>
+        <v>21330051920218</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
@@ -6712,19 +6715,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920217</v>
+        <v>21330051920218</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>62</v>
@@ -6732,19 +6735,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920217</v>
+        <v>21330051920219</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
@@ -6752,16 +6755,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920217</v>
+        <v>21330051920219</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -6772,16 +6775,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920218</v>
+        <v>21330051920220</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -6792,19 +6795,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920218</v>
+        <v>21330051920220</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>62</v>
@@ -6812,19 +6815,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920218</v>
+        <v>21330051920221</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -6832,19 +6835,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920219</v>
+        <v>21330051920221</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>62</v>
@@ -6852,19 +6855,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920219</v>
+        <v>21330051920230</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -6872,16 +6875,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920219</v>
+        <v>21330051920230</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -6892,16 +6895,16 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920220</v>
+        <v>21330051920231</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -6912,19 +6915,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920220</v>
+        <v>21330051920231</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
         <v>62</v>
@@ -6932,19 +6935,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920220</v>
+        <v>21330051920232</v>
       </c>
       <c r="B22" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
         <v>62</v>
@@ -6952,19 +6955,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920221</v>
+        <v>21330051920232</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>62</v>
@@ -6972,19 +6975,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920221</v>
+        <v>21330051920233</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>62</v>
@@ -6992,16 +6995,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920221</v>
+        <v>21330051920233</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -7012,16 +7015,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920230</v>
+        <v>21330051920042</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -7032,19 +7035,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920230</v>
+        <v>21330051920042</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
         <v>62</v>
@@ -7052,19 +7055,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920230</v>
+        <v>21330051920044</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
         <v>62</v>
@@ -7072,19 +7075,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920231</v>
+        <v>21330051920044</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
         <v>62</v>
@@ -7092,19 +7095,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920231</v>
+        <v>21330051920234</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
         <v>62</v>
@@ -7112,16 +7115,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920231</v>
+        <v>21330051920234</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
@@ -7132,16 +7135,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920232</v>
+        <v>21330051920235</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -7152,19 +7155,19 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920232</v>
+        <v>21330051920235</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" t="s">
         <v>62</v>
@@ -7172,19 +7175,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920232</v>
+        <v>21330051920236</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
         <v>62</v>
@@ -7192,19 +7195,19 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920233</v>
+        <v>21330051920236</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C35" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F35" t="s">
         <v>62</v>
@@ -7212,19 +7215,19 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920233</v>
+        <v>21330051920359</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C36" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E36" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
         <v>62</v>
@@ -7232,16 +7235,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920233</v>
+        <v>21330051920359</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E37" t="s">
         <v>5</v>
@@ -7252,16 +7255,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920042</v>
+        <v>21330051920237</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -7272,19 +7275,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920042</v>
+        <v>21330051920237</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F39" t="s">
         <v>62</v>
@@ -7292,19 +7295,19 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920042</v>
+        <v>21330051920239</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="D40" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="E40" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
         <v>62</v>
@@ -7312,19 +7315,19 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920044</v>
+        <v>21330051920239</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F41" t="s">
         <v>62</v>
@@ -7332,19 +7335,19 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920044</v>
+        <v>21330051920240</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D42" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
         <v>62</v>
@@ -7352,16 +7355,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920044</v>
+        <v>21330051920240</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C43" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E43" t="s">
         <v>5</v>
@@ -7372,16 +7375,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920234</v>
+        <v>21330051920049</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -7392,19 +7395,19 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920234</v>
+        <v>21330051920049</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F45" t="s">
         <v>62</v>
@@ -7412,19 +7415,19 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920234</v>
+        <v>21330051920241</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D46" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F46" t="s">
         <v>62</v>
@@ -7432,19 +7435,19 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920235</v>
+        <v>21330051920241</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D47" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F47" t="s">
         <v>62</v>
@@ -7452,19 +7455,19 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920235</v>
+        <v>21330051920242</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="D48" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
         <v>62</v>
@@ -7472,16 +7475,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920235</v>
+        <v>21330051920242</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C49" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E49" t="s">
         <v>5</v>
@@ -7492,16 +7495,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920236</v>
+        <v>21330051920244</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C50" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D50" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E50" t="s">
         <v>9</v>
@@ -7512,19 +7515,19 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920236</v>
+        <v>21330051920244</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F51" t="s">
         <v>62</v>
@@ -7532,19 +7535,19 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920236</v>
+        <v>21330051920246</v>
       </c>
       <c r="B52" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E52" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F52" t="s">
         <v>62</v>
@@ -7552,19 +7555,19 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>21330051920359</v>
+        <v>21330051920246</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D53" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F53" t="s">
         <v>62</v>
@@ -7572,19 +7575,19 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>21330051920359</v>
+        <v>21330051920247</v>
       </c>
       <c r="B54" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E54" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F54" t="s">
         <v>62</v>
@@ -7592,16 +7595,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>21330051920359</v>
+        <v>21330051920247</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="D55" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E55" t="s">
         <v>5</v>
@@ -7612,16 +7615,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>21330051920237</v>
+        <v>21330051920248</v>
       </c>
       <c r="B56" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="D56" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E56" t="s">
         <v>9</v>
@@ -7632,19 +7635,19 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>21330051920237</v>
+        <v>21330051920248</v>
       </c>
       <c r="B57" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="D57" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F57" t="s">
         <v>62</v>
@@ -7652,19 +7655,19 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>21330051920237</v>
+        <v>21330051920249</v>
       </c>
       <c r="B58" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E58" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F58" t="s">
         <v>62</v>
@@ -7672,19 +7675,19 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>21330051920239</v>
+        <v>21330051920249</v>
       </c>
       <c r="B59" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F59" t="s">
         <v>62</v>
@@ -7692,19 +7695,19 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>21330051920239</v>
+        <v>21330051920250</v>
       </c>
       <c r="B60" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="D60" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F60" t="s">
         <v>62</v>
@@ -7712,16 +7715,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>21330051920239</v>
+        <v>21330051920250</v>
       </c>
       <c r="B61" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="D61" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E61" t="s">
         <v>5</v>
@@ -7732,16 +7735,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>21330051920240</v>
+        <v>21330051920229</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C62" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="D62" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -7752,19 +7755,19 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>21330051920240</v>
+        <v>21330051920229</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C63" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="E63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F63" t="s">
         <v>62</v>
@@ -7772,19 +7775,19 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>21330051920240</v>
+        <v>21330051920228</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C64" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D64" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E64" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F64" t="s">
         <v>62</v>
@@ -7792,19 +7795,19 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>21330051920049</v>
+        <v>21330051920228</v>
       </c>
       <c r="B65" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C65" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="D65" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E65" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F65" t="s">
         <v>62</v>
@@ -7812,19 +7815,19 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>21330051920049</v>
+        <v>21330051920066</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C66" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D66" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E66" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F66" t="s">
         <v>62</v>
@@ -7832,16 +7835,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>21330051920049</v>
+        <v>21330051920066</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D67" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E67" t="s">
         <v>5</v>
@@ -7852,16 +7855,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>21330051920241</v>
+        <v>21330051920227</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="D68" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E68" t="s">
         <v>9</v>
@@ -7872,19 +7875,19 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>21330051920241</v>
+        <v>21330051920227</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C69" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="D69" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F69" t="s">
         <v>62</v>
@@ -7892,19 +7895,19 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>21330051920241</v>
+        <v>21330051920226</v>
       </c>
       <c r="B70" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="D70" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="E70" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F70" t="s">
         <v>62</v>
@@ -7912,19 +7915,19 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>21330051920242</v>
+        <v>21330051920226</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C71" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D71" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E71" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F71" t="s">
         <v>62</v>
@@ -7932,19 +7935,19 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>21330051920242</v>
+        <v>21330051920224</v>
       </c>
       <c r="B72" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C72" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D72" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E72" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F72" t="s">
         <v>62</v>
@@ -7952,16 +7955,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>21330051920242</v>
+        <v>21330051920224</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C73" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D73" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="E73" t="s">
         <v>5</v>
@@ -7972,16 +7975,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>21330051920244</v>
+        <v>21330051920223</v>
       </c>
       <c r="B74" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D74" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
@@ -7992,19 +7995,19 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>21330051920244</v>
+        <v>21330051920223</v>
       </c>
       <c r="B75" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C75" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D75" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="E75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F75" t="s">
         <v>62</v>
@@ -8012,19 +8015,19 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>21330051920244</v>
+        <v>21330051920222</v>
       </c>
       <c r="B76" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E76" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F76" t="s">
         <v>62</v>
@@ -8032,781 +8035,21 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>21330051920246</v>
+        <v>21330051920222</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C77" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D77" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E77" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F77" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920246</v>
-      </c>
-      <c r="B78" t="s">
-        <v>89</v>
-      </c>
-      <c r="C78" t="s">
-        <v>111</v>
-      </c>
-      <c r="D78" t="s">
-        <v>149</v>
-      </c>
-      <c r="E78" t="s">
-        <v>6</v>
-      </c>
-      <c r="F78" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920246</v>
-      </c>
-      <c r="B79" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" t="s">
-        <v>111</v>
-      </c>
-      <c r="D79" t="s">
-        <v>149</v>
-      </c>
-      <c r="E79" t="s">
-        <v>5</v>
-      </c>
-      <c r="F79" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920247</v>
-      </c>
-      <c r="B80" t="s">
-        <v>90</v>
-      </c>
-      <c r="C80" t="s">
-        <v>116</v>
-      </c>
-      <c r="D80" t="s">
-        <v>150</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920247</v>
-      </c>
-      <c r="B81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C81" t="s">
-        <v>116</v>
-      </c>
-      <c r="D81" t="s">
-        <v>150</v>
-      </c>
-      <c r="E81" t="s">
-        <v>6</v>
-      </c>
-      <c r="F81" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920247</v>
-      </c>
-      <c r="B82" t="s">
-        <v>90</v>
-      </c>
-      <c r="C82" t="s">
-        <v>116</v>
-      </c>
-      <c r="D82" t="s">
-        <v>150</v>
-      </c>
-      <c r="E82" t="s">
-        <v>5</v>
-      </c>
-      <c r="F82" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920248</v>
-      </c>
-      <c r="B83" t="s">
-        <v>91</v>
-      </c>
-      <c r="C83" t="s">
-        <v>117</v>
-      </c>
-      <c r="D83" t="s">
-        <v>151</v>
-      </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>21330051920248</v>
-      </c>
-      <c r="B84" t="s">
-        <v>91</v>
-      </c>
-      <c r="C84" t="s">
-        <v>117</v>
-      </c>
-      <c r="D84" t="s">
-        <v>151</v>
-      </c>
-      <c r="E84" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>21330051920248</v>
-      </c>
-      <c r="B85" t="s">
-        <v>91</v>
-      </c>
-      <c r="C85" t="s">
-        <v>117</v>
-      </c>
-      <c r="D85" t="s">
-        <v>151</v>
-      </c>
-      <c r="E85" t="s">
-        <v>5</v>
-      </c>
-      <c r="F85" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>21330051920249</v>
-      </c>
-      <c r="B86" t="s">
-        <v>92</v>
-      </c>
-      <c r="C86" t="s">
-        <v>118</v>
-      </c>
-      <c r="D86" t="s">
-        <v>152</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>21330051920249</v>
-      </c>
-      <c r="B87" t="s">
-        <v>92</v>
-      </c>
-      <c r="C87" t="s">
-        <v>118</v>
-      </c>
-      <c r="D87" t="s">
-        <v>152</v>
-      </c>
-      <c r="E87" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>21330051920249</v>
-      </c>
-      <c r="B88" t="s">
-        <v>92</v>
-      </c>
-      <c r="C88" t="s">
-        <v>118</v>
-      </c>
-      <c r="D88" t="s">
-        <v>152</v>
-      </c>
-      <c r="E88" t="s">
-        <v>5</v>
-      </c>
-      <c r="F88" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>21330051920250</v>
-      </c>
-      <c r="B89" t="s">
-        <v>93</v>
-      </c>
-      <c r="C89" t="s">
-        <v>119</v>
-      </c>
-      <c r="D89" t="s">
-        <v>153</v>
-      </c>
-      <c r="E89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>21330051920250</v>
-      </c>
-      <c r="B90" t="s">
-        <v>93</v>
-      </c>
-      <c r="C90" t="s">
-        <v>119</v>
-      </c>
-      <c r="D90" t="s">
-        <v>153</v>
-      </c>
-      <c r="E90" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>21330051920250</v>
-      </c>
-      <c r="B91" t="s">
-        <v>93</v>
-      </c>
-      <c r="C91" t="s">
-        <v>119</v>
-      </c>
-      <c r="D91" t="s">
-        <v>153</v>
-      </c>
-      <c r="E91" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>21330051920229</v>
-      </c>
-      <c r="B92" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" t="s">
-        <v>88</v>
-      </c>
-      <c r="D92" t="s">
-        <v>154</v>
-      </c>
-      <c r="E92" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>21330051920229</v>
-      </c>
-      <c r="B93" t="s">
-        <v>93</v>
-      </c>
-      <c r="C93" t="s">
-        <v>88</v>
-      </c>
-      <c r="D93" t="s">
-        <v>154</v>
-      </c>
-      <c r="E93" t="s">
-        <v>6</v>
-      </c>
-      <c r="F93" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>21330051920229</v>
-      </c>
-      <c r="B94" t="s">
-        <v>93</v>
-      </c>
-      <c r="C94" t="s">
-        <v>88</v>
-      </c>
-      <c r="D94" t="s">
-        <v>154</v>
-      </c>
-      <c r="E94" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>21330051920228</v>
-      </c>
-      <c r="B95" t="s">
-        <v>94</v>
-      </c>
-      <c r="C95" t="s">
-        <v>120</v>
-      </c>
-      <c r="D95" t="s">
-        <v>155</v>
-      </c>
-      <c r="E95" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>21330051920228</v>
-      </c>
-      <c r="B96" t="s">
-        <v>94</v>
-      </c>
-      <c r="C96" t="s">
-        <v>120</v>
-      </c>
-      <c r="D96" t="s">
-        <v>155</v>
-      </c>
-      <c r="E96" t="s">
-        <v>6</v>
-      </c>
-      <c r="F96" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>21330051920228</v>
-      </c>
-      <c r="B97" t="s">
-        <v>94</v>
-      </c>
-      <c r="C97" t="s">
-        <v>120</v>
-      </c>
-      <c r="D97" t="s">
-        <v>155</v>
-      </c>
-      <c r="E97" t="s">
-        <v>5</v>
-      </c>
-      <c r="F97" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>21330051920066</v>
-      </c>
-      <c r="B98" t="s">
-        <v>95</v>
-      </c>
-      <c r="C98" t="s">
-        <v>81</v>
-      </c>
-      <c r="D98" t="s">
-        <v>156</v>
-      </c>
-      <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>21330051920066</v>
-      </c>
-      <c r="B99" t="s">
-        <v>95</v>
-      </c>
-      <c r="C99" t="s">
-        <v>81</v>
-      </c>
-      <c r="D99" t="s">
-        <v>156</v>
-      </c>
-      <c r="E99" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>21330051920066</v>
-      </c>
-      <c r="B100" t="s">
-        <v>95</v>
-      </c>
-      <c r="C100" t="s">
-        <v>81</v>
-      </c>
-      <c r="D100" t="s">
-        <v>156</v>
-      </c>
-      <c r="E100" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>21330051920227</v>
-      </c>
-      <c r="B101" t="s">
-        <v>96</v>
-      </c>
-      <c r="C101" t="s">
-        <v>121</v>
-      </c>
-      <c r="D101" t="s">
-        <v>157</v>
-      </c>
-      <c r="E101" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>21330051920227</v>
-      </c>
-      <c r="B102" t="s">
-        <v>96</v>
-      </c>
-      <c r="C102" t="s">
-        <v>121</v>
-      </c>
-      <c r="D102" t="s">
-        <v>157</v>
-      </c>
-      <c r="E102" t="s">
-        <v>6</v>
-      </c>
-      <c r="F102" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>21330051920227</v>
-      </c>
-      <c r="B103" t="s">
-        <v>96</v>
-      </c>
-      <c r="C103" t="s">
-        <v>121</v>
-      </c>
-      <c r="D103" t="s">
-        <v>157</v>
-      </c>
-      <c r="E103" t="s">
-        <v>5</v>
-      </c>
-      <c r="F103" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>21330051920226</v>
-      </c>
-      <c r="B104" t="s">
-        <v>97</v>
-      </c>
-      <c r="C104" t="s">
-        <v>122</v>
-      </c>
-      <c r="D104" t="s">
-        <v>158</v>
-      </c>
-      <c r="E104" t="s">
-        <v>9</v>
-      </c>
-      <c r="F104" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>21330051920226</v>
-      </c>
-      <c r="B105" t="s">
-        <v>97</v>
-      </c>
-      <c r="C105" t="s">
-        <v>122</v>
-      </c>
-      <c r="D105" t="s">
-        <v>158</v>
-      </c>
-      <c r="E105" t="s">
-        <v>6</v>
-      </c>
-      <c r="F105" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>21330051920226</v>
-      </c>
-      <c r="B106" t="s">
-        <v>97</v>
-      </c>
-      <c r="C106" t="s">
-        <v>122</v>
-      </c>
-      <c r="D106" t="s">
-        <v>158</v>
-      </c>
-      <c r="E106" t="s">
-        <v>5</v>
-      </c>
-      <c r="F106" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>21330051920224</v>
-      </c>
-      <c r="B107" t="s">
-        <v>98</v>
-      </c>
-      <c r="C107" t="s">
-        <v>104</v>
-      </c>
-      <c r="D107" t="s">
-        <v>159</v>
-      </c>
-      <c r="E107" t="s">
-        <v>9</v>
-      </c>
-      <c r="F107" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>21330051920224</v>
-      </c>
-      <c r="B108" t="s">
-        <v>98</v>
-      </c>
-      <c r="C108" t="s">
-        <v>104</v>
-      </c>
-      <c r="D108" t="s">
-        <v>159</v>
-      </c>
-      <c r="E108" t="s">
-        <v>6</v>
-      </c>
-      <c r="F108" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>21330051920224</v>
-      </c>
-      <c r="B109" t="s">
-        <v>98</v>
-      </c>
-      <c r="C109" t="s">
-        <v>104</v>
-      </c>
-      <c r="D109" t="s">
-        <v>159</v>
-      </c>
-      <c r="E109" t="s">
-        <v>5</v>
-      </c>
-      <c r="F109" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>21330051920223</v>
-      </c>
-      <c r="B110" t="s">
-        <v>99</v>
-      </c>
-      <c r="C110" t="s">
-        <v>123</v>
-      </c>
-      <c r="D110" t="s">
-        <v>160</v>
-      </c>
-      <c r="E110" t="s">
-        <v>9</v>
-      </c>
-      <c r="F110" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>21330051920223</v>
-      </c>
-      <c r="B111" t="s">
-        <v>99</v>
-      </c>
-      <c r="C111" t="s">
-        <v>123</v>
-      </c>
-      <c r="D111" t="s">
-        <v>160</v>
-      </c>
-      <c r="E111" t="s">
-        <v>6</v>
-      </c>
-      <c r="F111" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>21330051920223</v>
-      </c>
-      <c r="B112" t="s">
-        <v>99</v>
-      </c>
-      <c r="C112" t="s">
-        <v>123</v>
-      </c>
-      <c r="D112" t="s">
-        <v>160</v>
-      </c>
-      <c r="E112" t="s">
-        <v>5</v>
-      </c>
-      <c r="F112" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>21330051920222</v>
-      </c>
-      <c r="B113" t="s">
-        <v>100</v>
-      </c>
-      <c r="C113" t="s">
-        <v>109</v>
-      </c>
-      <c r="D113" t="s">
-        <v>161</v>
-      </c>
-      <c r="E113" t="s">
-        <v>9</v>
-      </c>
-      <c r="F113" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>21330051920222</v>
-      </c>
-      <c r="B114" t="s">
-        <v>100</v>
-      </c>
-      <c r="C114" t="s">
-        <v>109</v>
-      </c>
-      <c r="D114" t="s">
-        <v>161</v>
-      </c>
-      <c r="E114" t="s">
-        <v>6</v>
-      </c>
-      <c r="F114" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>21330051920222</v>
-      </c>
-      <c r="B115" t="s">
-        <v>100</v>
-      </c>
-      <c r="C115" t="s">
-        <v>109</v>
-      </c>
-      <c r="D115" t="s">
-        <v>161</v>
-      </c>
-      <c r="E115" t="s">
-        <v>5</v>
-      </c>
-      <c r="F115" t="s">
         <v>62</v>
       </c>
     </row>
@@ -8855,7 +8098,7 @@
         <v>124</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8872,7 +8115,7 @@
         <v>125</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8889,7 +8132,7 @@
         <v>126</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8906,7 +8149,7 @@
         <v>127</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8923,7 +8166,7 @@
         <v>128</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8940,7 +8183,7 @@
         <v>129</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8957,7 +8200,7 @@
         <v>130</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8974,7 +8217,7 @@
         <v>131</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8991,7 +8234,7 @@
         <v>132</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9008,7 +8251,7 @@
         <v>133</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -9025,7 +8268,7 @@
         <v>134</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -9042,7 +8285,7 @@
         <v>135</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -9059,7 +8302,7 @@
         <v>136</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -9076,7 +8319,7 @@
         <v>137</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -9093,7 +8336,7 @@
         <v>138</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -9110,7 +8353,7 @@
         <v>139</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -9127,7 +8370,7 @@
         <v>140</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -9144,7 +8387,7 @@
         <v>141</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -9161,7 +8404,7 @@
         <v>142</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -9178,7 +8421,7 @@
         <v>143</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -9195,7 +8438,7 @@
         <v>144</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -9212,7 +8455,7 @@
         <v>145</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9229,7 +8472,7 @@
         <v>146</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9246,7 +8489,7 @@
         <v>147</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9263,7 +8506,7 @@
         <v>148</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9280,7 +8523,7 @@
         <v>149</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9297,7 +8540,7 @@
         <v>150</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9314,7 +8557,7 @@
         <v>151</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9331,7 +8574,7 @@
         <v>152</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9348,7 +8591,7 @@
         <v>153</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9365,7 +8608,7 @@
         <v>154</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9382,7 +8625,7 @@
         <v>155</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9399,7 +8642,7 @@
         <v>156</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9416,7 +8659,7 @@
         <v>157</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9433,7 +8676,7 @@
         <v>158</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9450,7 +8693,7 @@
         <v>159</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9467,7 +8710,7 @@
         <v>160</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9484,7 +8727,7 @@
         <v>161</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9494,7 +8737,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9524,6 +8767,1156 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920215</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920215</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920216</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920216</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920033</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920033</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920217</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920217</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920220</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920220</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920221</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920221</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920230</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920230</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920231</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920231</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920232</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>21330051920232</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>21330051920233</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920233</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>21330051920042</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>21330051920042</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920236</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>21330051920236</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920049</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920049</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920241</v>
+      </c>
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920241</v>
+      </c>
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920244</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" t="s">
+        <v>148</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>21330051920244</v>
+      </c>
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>21330051920246</v>
+      </c>
+      <c r="B32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>21330051920246</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920247</v>
+      </c>
+      <c r="B34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" t="s">
+        <v>150</v>
+      </c>
+      <c r="E34" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" t="s">
+        <v>62</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>21330051920247</v>
+      </c>
+      <c r="B35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" t="s">
+        <v>150</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920248</v>
+      </c>
+      <c r="B36" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" t="s">
+        <v>151</v>
+      </c>
+      <c r="E36" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>21330051920248</v>
+      </c>
+      <c r="B37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" t="s">
+        <v>151</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920250</v>
+      </c>
+      <c r="B38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" t="s">
+        <v>119</v>
+      </c>
+      <c r="D38" t="s">
+        <v>153</v>
+      </c>
+      <c r="E38" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920250</v>
+      </c>
+      <c r="B39" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>21330051920229</v>
+      </c>
+      <c r="B40" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" t="s">
+        <v>154</v>
+      </c>
+      <c r="E40" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>21330051920229</v>
+      </c>
+      <c r="B41" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>21330051920228</v>
+      </c>
+      <c r="B42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" t="s">
+        <v>155</v>
+      </c>
+      <c r="E42" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" t="s">
+        <v>62</v>
+      </c>
+      <c r="G42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>21330051920228</v>
+      </c>
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" t="s">
+        <v>155</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>62</v>
+      </c>
+      <c r="G43">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>21330051920066</v>
+      </c>
+      <c r="B44" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" t="s">
+        <v>81</v>
+      </c>
+      <c r="D44" t="s">
+        <v>156</v>
+      </c>
+      <c r="E44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
+        <v>62</v>
+      </c>
+      <c r="G44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>21330051920066</v>
+      </c>
+      <c r="B45" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" t="s">
+        <v>81</v>
+      </c>
+      <c r="D45" t="s">
+        <v>156</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>62</v>
+      </c>
+      <c r="G45">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>21330051920227</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" t="s">
+        <v>121</v>
+      </c>
+      <c r="D46" t="s">
+        <v>157</v>
+      </c>
+      <c r="E46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>21330051920227</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" t="s">
+        <v>157</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>62</v>
+      </c>
+      <c r="G47">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>21330051920226</v>
+      </c>
+      <c r="B48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E48" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>21330051920226</v>
+      </c>
+      <c r="B49" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>62</v>
+      </c>
+      <c r="G49">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>21330051920224</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>21330051920224</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>62</v>
+      </c>
+      <c r="G51">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="162">
   <si>
     <t>Materia</t>
   </si>
@@ -1002,7 +1002,7 @@
         <v>8</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>9</v>
@@ -1056,7 +1056,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1079,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -1133,7 +1133,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1156,7 +1156,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>6</v>
@@ -1210,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1233,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>6</v>
@@ -1287,7 +1287,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1310,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>7</v>
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1387,7 +1387,7 @@
         <v>8</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1441,7 +1441,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1464,7 +1464,7 @@
         <v>9</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1518,7 +1518,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1541,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>9</v>
@@ -1595,7 +1595,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1618,7 +1618,7 @@
         <v>8</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1672,7 +1672,7 @@
         <v>8</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1695,7 +1695,7 @@
         <v>9</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>9</v>
@@ -1749,7 +1749,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1772,7 +1772,7 @@
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1826,7 +1826,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1849,7 +1849,7 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1926,7 +1926,7 @@
         <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G16">
         <v>10</v>
@@ -1980,7 +1980,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -2003,7 +2003,7 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -2057,7 +2057,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2080,7 +2080,7 @@
         <v>5</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -2134,7 +2134,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2157,7 +2157,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G19">
         <v>6</v>
@@ -2211,7 +2211,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2234,7 +2234,7 @@
         <v>9</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -2288,7 +2288,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2311,7 +2311,7 @@
         <v>5</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2365,7 +2365,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2388,7 +2388,7 @@
         <v>9</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2442,7 +2442,7 @@
         <v>9</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2465,7 +2465,7 @@
         <v>5</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -2519,7 +2519,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y23">
         <v>5</v>
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G24">
         <v>7</v>
@@ -2596,7 +2596,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2619,7 +2619,7 @@
         <v>9</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G25">
         <v>10</v>
@@ -2673,7 +2673,7 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2696,7 +2696,7 @@
         <v>9</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>9</v>
@@ -2750,7 +2750,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -2827,7 +2827,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2850,7 +2850,7 @@
         <v>8</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G28">
         <v>6</v>
@@ -2904,7 +2904,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2927,7 +2927,7 @@
         <v>8</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>7</v>
@@ -2981,7 +2981,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3004,7 +3004,7 @@
         <v>8</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G30">
         <v>6</v>
@@ -3058,7 +3058,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>6</v>
@@ -3081,7 +3081,7 @@
         <v>8</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -3135,7 +3135,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3158,7 +3158,7 @@
         <v>9</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>9</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3235,7 +3235,7 @@
         <v>8</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>10</v>
@@ -3289,7 +3289,7 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3312,7 +3312,7 @@
         <v>7</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G34">
         <v>7</v>
@@ -3366,7 +3366,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3389,7 +3389,7 @@
         <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>9</v>
@@ -3443,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -3466,7 +3466,7 @@
         <v>6</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>7</v>
@@ -3520,7 +3520,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3543,7 +3543,7 @@
         <v>8</v>
       </c>
       <c r="F37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G37">
         <v>6</v>
@@ -3597,7 +3597,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3620,7 +3620,7 @@
         <v>9</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G38">
         <v>10</v>
@@ -3674,7 +3674,7 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -3697,7 +3697,7 @@
         <v>9</v>
       </c>
       <c r="F39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G39">
         <v>7</v>
@@ -3751,7 +3751,7 @@
         <v>9</v>
       </c>
       <c r="X39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -3774,7 +3774,7 @@
         <v>8</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -3828,7 +3828,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3851,7 +3851,7 @@
         <v>5</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -3905,7 +3905,7 @@
         <v>5</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y41">
         <v>5</v>
@@ -4038,7 +4038,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>106.7</v>
@@ -4097,7 +4097,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>106.7</v>
@@ -4156,7 +4156,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>106.7</v>
@@ -4215,7 +4215,7 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>106.7</v>
@@ -4274,7 +4274,7 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>106.7</v>
@@ -4333,7 +4333,7 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>106.7</v>
@@ -4392,7 +4392,7 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>106.7</v>
@@ -4451,7 +4451,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>106.7</v>
@@ -4510,7 +4510,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>106.7</v>
@@ -4569,7 +4569,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>106.7</v>
@@ -4628,7 +4628,7 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>106.7</v>
@@ -4687,7 +4687,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>106.7</v>
@@ -4746,7 +4746,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>106.7</v>
@@ -4805,7 +4805,7 @@
         <v>90</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>80</v>
@@ -4864,7 +4864,7 @@
         <v>90</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>106.7</v>
@@ -4923,7 +4923,7 @@
         <v>90</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>106.7</v>
@@ -4982,7 +4982,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>106.7</v>
@@ -5041,7 +5041,7 @@
         <v>90</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G21">
         <v>86.7</v>
@@ -5100,7 +5100,7 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>106.7</v>
@@ -5159,7 +5159,7 @@
         <v>90</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5218,7 +5218,7 @@
         <v>90</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G24">
         <v>106.7</v>
@@ -5277,7 +5277,7 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>106.7</v>
@@ -5336,7 +5336,7 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>106.7</v>
@@ -5395,7 +5395,7 @@
         <v>90</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5454,7 +5454,7 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>106.7</v>
@@ -5513,7 +5513,7 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>106.7</v>
@@ -5572,7 +5572,7 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>106.7</v>
@@ -5631,7 +5631,7 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>106.7</v>
@@ -5690,7 +5690,7 @@
         <v>100</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>106.7</v>
@@ -5749,7 +5749,7 @@
         <v>100</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>106.7</v>
@@ -5808,7 +5808,7 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>106.7</v>
@@ -5867,7 +5867,7 @@
         <v>100</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>106.7</v>
@@ -5926,7 +5926,7 @@
         <v>100</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>106.7</v>
@@ -5985,7 +5985,7 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37">
         <v>106.7</v>
@@ -6044,7 +6044,7 @@
         <v>100</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38">
         <v>106.7</v>
@@ -6103,7 +6103,7 @@
         <v>100</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39">
         <v>106.7</v>
@@ -6162,7 +6162,7 @@
         <v>100</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G40">
         <v>106.7</v>
@@ -6221,7 +6221,7 @@
         <v>100</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G41">
         <v>106.7</v>
@@ -6315,7 +6315,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6344,7 +6344,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -6353,27 +6353,30 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>26.32</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -6382,19 +6385,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="G4">
-        <v>26.32</v>
+        <v>21.05</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6405,7 +6408,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6414,19 +6417,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>78.95</v>
+        <v>81.58</v>
       </c>
       <c r="G5">
-        <v>21.05</v>
+        <v>18.42</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6506,7 +6509,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6547,7 +6550,7 @@
         <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
@@ -6555,16 +6558,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920215</v>
+        <v>21330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -6575,19 +6578,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920216</v>
+        <v>21330051920033</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
@@ -6595,16 +6598,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920216</v>
+        <v>21330051920217</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -6615,19 +6618,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920033</v>
+        <v>21330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
@@ -6635,16 +6638,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920033</v>
+        <v>21330051920219</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -6655,19 +6658,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920217</v>
+        <v>21330051920220</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>62</v>
@@ -6675,16 +6678,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920217</v>
+        <v>21330051920221</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -6695,19 +6698,19 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920218</v>
+        <v>21330051920230</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
@@ -6715,16 +6718,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920218</v>
+        <v>21330051920231</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -6735,19 +6738,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920219</v>
+        <v>21330051920232</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
@@ -6755,16 +6758,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920219</v>
+        <v>21330051920233</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
@@ -6775,19 +6778,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920220</v>
+        <v>21330051920042</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
@@ -6795,16 +6798,16 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920220</v>
+        <v>21330051920044</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -6815,19 +6818,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920221</v>
+        <v>21330051920234</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -6835,16 +6838,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920221</v>
+        <v>21330051920235</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
@@ -6855,19 +6858,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920230</v>
+        <v>21330051920236</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -6875,16 +6878,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920230</v>
+        <v>21330051920359</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
         <v>82</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
@@ -6895,19 +6898,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920231</v>
+        <v>21330051920237</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -6915,16 +6918,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920231</v>
+        <v>21330051920239</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E21" t="s">
         <v>5</v>
@@ -6935,19 +6938,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920232</v>
+        <v>21330051920240</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
         <v>62</v>
@@ -6955,16 +6958,16 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920232</v>
+        <v>21330051920049</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
@@ -6975,19 +6978,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920233</v>
+        <v>21330051920241</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
         <v>62</v>
@@ -6995,16 +6998,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920233</v>
+        <v>21330051920242</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
@@ -7015,19 +7018,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920042</v>
+        <v>21330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
         <v>62</v>
@@ -7035,16 +7038,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920042</v>
+        <v>21330051920246</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
@@ -7055,19 +7058,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920044</v>
+        <v>21330051920247</v>
       </c>
       <c r="B28" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
         <v>62</v>
@@ -7075,16 +7078,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920044</v>
+        <v>21330051920248</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="E29" t="s">
         <v>5</v>
@@ -7095,19 +7098,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920234</v>
+        <v>21330051920249</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
         <v>62</v>
@@ -7115,16 +7118,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920234</v>
+        <v>21330051920250</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
         <v>5</v>
@@ -7135,19 +7138,19 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920235</v>
+        <v>21330051920229</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F32" t="s">
         <v>62</v>
@@ -7155,16 +7158,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920235</v>
+        <v>21330051920228</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="E33" t="s">
         <v>5</v>
@@ -7175,19 +7178,19 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920236</v>
+        <v>21330051920066</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F34" t="s">
         <v>62</v>
@@ -7195,16 +7198,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920236</v>
+        <v>21330051920227</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="E35" t="s">
         <v>5</v>
@@ -7215,19 +7218,19 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920359</v>
+        <v>21330051920226</v>
       </c>
       <c r="B36" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F36" t="s">
         <v>62</v>
@@ -7235,16 +7238,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920359</v>
+        <v>21330051920224</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="E37" t="s">
         <v>5</v>
@@ -7255,19 +7258,19 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920237</v>
+        <v>21330051920223</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F38" t="s">
         <v>62</v>
@@ -7275,781 +7278,21 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920237</v>
+        <v>21330051920222</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E39" t="s">
         <v>5</v>
       </c>
       <c r="F39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920239</v>
-      </c>
-      <c r="B40" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" t="s">
-        <v>143</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920239</v>
-      </c>
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" t="s">
-        <v>143</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920240</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" t="s">
-        <v>144</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920240</v>
-      </c>
-      <c r="B43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" t="s">
-        <v>144</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920049</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" t="s">
-        <v>145</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920049</v>
-      </c>
-      <c r="B45" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>82</v>
-      </c>
-      <c r="D45" t="s">
-        <v>145</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920241</v>
-      </c>
-      <c r="B46" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" t="s">
-        <v>81</v>
-      </c>
-      <c r="D46" t="s">
-        <v>146</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920241</v>
-      </c>
-      <c r="B47" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" t="s">
-        <v>146</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920242</v>
-      </c>
-      <c r="B48" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" t="s">
-        <v>115</v>
-      </c>
-      <c r="D48" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920242</v>
-      </c>
-      <c r="B49" t="s">
-        <v>87</v>
-      </c>
-      <c r="C49" t="s">
-        <v>115</v>
-      </c>
-      <c r="D49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920244</v>
-      </c>
-      <c r="B50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" t="s">
-        <v>108</v>
-      </c>
-      <c r="D50" t="s">
-        <v>148</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920244</v>
-      </c>
-      <c r="B51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" t="s">
-        <v>148</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920246</v>
-      </c>
-      <c r="B52" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" t="s">
-        <v>111</v>
-      </c>
-      <c r="D52" t="s">
-        <v>149</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920246</v>
-      </c>
-      <c r="B53" t="s">
-        <v>89</v>
-      </c>
-      <c r="C53" t="s">
-        <v>111</v>
-      </c>
-      <c r="D53" t="s">
-        <v>149</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920247</v>
-      </c>
-      <c r="B54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C54" t="s">
-        <v>116</v>
-      </c>
-      <c r="D54" t="s">
-        <v>150</v>
-      </c>
-      <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920247</v>
-      </c>
-      <c r="B55" t="s">
-        <v>90</v>
-      </c>
-      <c r="C55" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" t="s">
-        <v>150</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920248</v>
-      </c>
-      <c r="B56" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" t="s">
-        <v>117</v>
-      </c>
-      <c r="D56" t="s">
-        <v>151</v>
-      </c>
-      <c r="E56" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920248</v>
-      </c>
-      <c r="B57" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" t="s">
-        <v>117</v>
-      </c>
-      <c r="D57" t="s">
-        <v>151</v>
-      </c>
-      <c r="E57" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920249</v>
-      </c>
-      <c r="B58" t="s">
-        <v>92</v>
-      </c>
-      <c r="C58" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" t="s">
-        <v>152</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920249</v>
-      </c>
-      <c r="B59" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" t="s">
-        <v>152</v>
-      </c>
-      <c r="E59" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920250</v>
-      </c>
-      <c r="B60" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" t="s">
-        <v>119</v>
-      </c>
-      <c r="D60" t="s">
-        <v>153</v>
-      </c>
-      <c r="E60" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920250</v>
-      </c>
-      <c r="B61" t="s">
-        <v>93</v>
-      </c>
-      <c r="C61" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" t="s">
-        <v>153</v>
-      </c>
-      <c r="E61" t="s">
-        <v>5</v>
-      </c>
-      <c r="F61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920229</v>
-      </c>
-      <c r="B62" t="s">
-        <v>93</v>
-      </c>
-      <c r="C62" t="s">
-        <v>88</v>
-      </c>
-      <c r="D62" t="s">
-        <v>154</v>
-      </c>
-      <c r="E62" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920229</v>
-      </c>
-      <c r="B63" t="s">
-        <v>93</v>
-      </c>
-      <c r="C63" t="s">
-        <v>88</v>
-      </c>
-      <c r="D63" t="s">
-        <v>154</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920228</v>
-      </c>
-      <c r="B64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C64" t="s">
-        <v>120</v>
-      </c>
-      <c r="D64" t="s">
-        <v>155</v>
-      </c>
-      <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920228</v>
-      </c>
-      <c r="B65" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" t="s">
-        <v>120</v>
-      </c>
-      <c r="D65" t="s">
-        <v>155</v>
-      </c>
-      <c r="E65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F65" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920066</v>
-      </c>
-      <c r="B66" t="s">
-        <v>95</v>
-      </c>
-      <c r="C66" t="s">
-        <v>81</v>
-      </c>
-      <c r="D66" t="s">
-        <v>156</v>
-      </c>
-      <c r="E66" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920066</v>
-      </c>
-      <c r="B67" t="s">
-        <v>95</v>
-      </c>
-      <c r="C67" t="s">
-        <v>81</v>
-      </c>
-      <c r="D67" t="s">
-        <v>156</v>
-      </c>
-      <c r="E67" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920227</v>
-      </c>
-      <c r="B68" t="s">
-        <v>96</v>
-      </c>
-      <c r="C68" t="s">
-        <v>121</v>
-      </c>
-      <c r="D68" t="s">
-        <v>157</v>
-      </c>
-      <c r="E68" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920227</v>
-      </c>
-      <c r="B69" t="s">
-        <v>96</v>
-      </c>
-      <c r="C69" t="s">
-        <v>121</v>
-      </c>
-      <c r="D69" t="s">
-        <v>157</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920226</v>
-      </c>
-      <c r="B70" t="s">
-        <v>97</v>
-      </c>
-      <c r="C70" t="s">
-        <v>122</v>
-      </c>
-      <c r="D70" t="s">
-        <v>158</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920226</v>
-      </c>
-      <c r="B71" t="s">
-        <v>97</v>
-      </c>
-      <c r="C71" t="s">
-        <v>122</v>
-      </c>
-      <c r="D71" t="s">
-        <v>158</v>
-      </c>
-      <c r="E71" t="s">
-        <v>5</v>
-      </c>
-      <c r="F71" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920224</v>
-      </c>
-      <c r="B72" t="s">
-        <v>98</v>
-      </c>
-      <c r="C72" t="s">
-        <v>104</v>
-      </c>
-      <c r="D72" t="s">
-        <v>159</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920224</v>
-      </c>
-      <c r="B73" t="s">
-        <v>98</v>
-      </c>
-      <c r="C73" t="s">
-        <v>104</v>
-      </c>
-      <c r="D73" t="s">
-        <v>159</v>
-      </c>
-      <c r="E73" t="s">
-        <v>5</v>
-      </c>
-      <c r="F73" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920223</v>
-      </c>
-      <c r="B74" t="s">
-        <v>99</v>
-      </c>
-      <c r="C74" t="s">
-        <v>123</v>
-      </c>
-      <c r="D74" t="s">
-        <v>160</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920223</v>
-      </c>
-      <c r="B75" t="s">
-        <v>99</v>
-      </c>
-      <c r="C75" t="s">
-        <v>123</v>
-      </c>
-      <c r="D75" t="s">
-        <v>160</v>
-      </c>
-      <c r="E75" t="s">
-        <v>5</v>
-      </c>
-      <c r="F75" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920222</v>
-      </c>
-      <c r="B76" t="s">
-        <v>100</v>
-      </c>
-      <c r="C76" t="s">
-        <v>109</v>
-      </c>
-      <c r="D76" t="s">
-        <v>161</v>
-      </c>
-      <c r="E76" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920222</v>
-      </c>
-      <c r="B77" t="s">
-        <v>100</v>
-      </c>
-      <c r="C77" t="s">
-        <v>109</v>
-      </c>
-      <c r="D77" t="s">
-        <v>161</v>
-      </c>
-      <c r="E77" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" t="s">
         <v>62</v>
       </c>
     </row>
@@ -8098,7 +7341,7 @@
         <v>124</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8115,7 +7358,7 @@
         <v>125</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8132,7 +7375,7 @@
         <v>126</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8149,7 +7392,7 @@
         <v>127</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8166,7 +7409,7 @@
         <v>128</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8183,7 +7426,7 @@
         <v>129</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8200,7 +7443,7 @@
         <v>130</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8217,7 +7460,7 @@
         <v>131</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8234,7 +7477,7 @@
         <v>132</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8251,7 +7494,7 @@
         <v>133</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8268,7 +7511,7 @@
         <v>134</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8285,7 +7528,7 @@
         <v>135</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8302,7 +7545,7 @@
         <v>136</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8319,7 +7562,7 @@
         <v>137</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8336,7 +7579,7 @@
         <v>138</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8353,7 +7596,7 @@
         <v>139</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8370,7 +7613,7 @@
         <v>140</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8387,7 +7630,7 @@
         <v>141</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8404,7 +7647,7 @@
         <v>142</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8421,7 +7664,7 @@
         <v>143</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8438,7 +7681,7 @@
         <v>144</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8455,7 +7698,7 @@
         <v>145</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8472,7 +7715,7 @@
         <v>146</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8489,7 +7732,7 @@
         <v>147</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8506,7 +7749,7 @@
         <v>148</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8523,7 +7766,7 @@
         <v>149</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8540,7 +7783,7 @@
         <v>150</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8557,7 +7800,7 @@
         <v>151</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8574,7 +7817,7 @@
         <v>152</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8591,7 +7834,7 @@
         <v>153</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8608,7 +7851,7 @@
         <v>154</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8625,7 +7868,7 @@
         <v>155</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8642,7 +7885,7 @@
         <v>156</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8659,7 +7902,7 @@
         <v>157</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8676,7 +7919,7 @@
         <v>158</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8693,7 +7936,7 @@
         <v>159</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8710,7 +7953,7 @@
         <v>160</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8727,7 +7970,7 @@
         <v>161</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8737,7 +7980,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8769,16 +8012,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920215</v>
+        <v>21330051920218</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -8792,39 +8035,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920215</v>
+        <v>21330051920218</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>62</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920216</v>
+        <v>21330051920219</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -8838,39 +8081,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920216</v>
+        <v>21330051920219</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>62</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920033</v>
+        <v>21330051920044</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -8884,39 +8127,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920033</v>
+        <v>21330051920044</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>62</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920217</v>
+        <v>21330051920239</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -8930,39 +8173,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920217</v>
+        <v>21330051920239</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920220</v>
+        <v>21330051920249</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -8976,39 +8219,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920220</v>
+        <v>21330051920249</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>62</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920221</v>
+        <v>21330051920223</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -9022,39 +8265,39 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920221</v>
+        <v>21330051920223</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>62</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920230</v>
+        <v>21330051920215</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -9068,19 +8311,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920230</v>
+        <v>21330051920216</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>62</v>
@@ -9091,16 +8334,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920231</v>
+        <v>21330051920033</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
@@ -9114,19 +8357,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920231</v>
+        <v>21330051920217</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>62</v>
@@ -9137,16 +8380,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920232</v>
+        <v>21330051920220</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -9160,19 +8403,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920232</v>
+        <v>21330051920221</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
         <v>62</v>
@@ -9183,16 +8426,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920233</v>
+        <v>21330051920230</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -9206,19 +8449,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920233</v>
+        <v>21330051920231</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
         <v>62</v>
@@ -9229,16 +8472,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920042</v>
+        <v>21330051920232</v>
       </c>
       <c r="B22" t="s">
         <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
@@ -9252,19 +8495,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920042</v>
+        <v>21330051920233</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>62</v>
@@ -9275,16 +8518,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920236</v>
+        <v>21330051920042</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -9310,7 +8553,7 @@
         <v>140</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
         <v>62</v>
@@ -9344,19 +8587,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920049</v>
+        <v>21330051920241</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
         <v>62</v>
@@ -9367,16 +8610,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920241</v>
+        <v>21330051920244</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
@@ -9390,19 +8633,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920241</v>
+        <v>21330051920246</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
         <v>62</v>
@@ -9413,16 +8656,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920244</v>
+        <v>21330051920247</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
         <v>5</v>
@@ -9436,19 +8679,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920244</v>
+        <v>21330051920248</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F31" t="s">
         <v>62</v>
@@ -9459,16 +8702,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920246</v>
+        <v>21330051920250</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
         <v>5</v>
@@ -9482,19 +8725,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>21330051920246</v>
+        <v>21330051920229</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F33" t="s">
         <v>62</v>
@@ -9505,16 +8748,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>21330051920247</v>
+        <v>21330051920228</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
@@ -9528,19 +8771,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>21330051920247</v>
+        <v>21330051920066</v>
       </c>
       <c r="B35" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F35" t="s">
         <v>62</v>
@@ -9551,16 +8794,16 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>21330051920248</v>
+        <v>21330051920227</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D36" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E36" t="s">
         <v>5</v>
@@ -9574,19 +8817,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>21330051920248</v>
+        <v>21330051920226</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F37" t="s">
         <v>62</v>
@@ -9597,16 +8840,16 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>21330051920250</v>
+        <v>21330051920224</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D38" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E38" t="s">
         <v>5</v>
@@ -9615,305 +8858,6 @@
         <v>62</v>
       </c>
       <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920250</v>
-      </c>
-      <c r="B39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" t="s">
-        <v>153</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920229</v>
-      </c>
-      <c r="B40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" t="s">
-        <v>154</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920229</v>
-      </c>
-      <c r="B41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" t="s">
-        <v>154</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920228</v>
-      </c>
-      <c r="B42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" t="s">
-        <v>155</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920228</v>
-      </c>
-      <c r="B43" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" t="s">
-        <v>155</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>62</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920066</v>
-      </c>
-      <c r="B44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" t="s">
-        <v>81</v>
-      </c>
-      <c r="D44" t="s">
-        <v>156</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>62</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920066</v>
-      </c>
-      <c r="B45" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" t="s">
-        <v>81</v>
-      </c>
-      <c r="D45" t="s">
-        <v>156</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>62</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920227</v>
-      </c>
-      <c r="B46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>121</v>
-      </c>
-      <c r="D46" t="s">
-        <v>157</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>62</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920227</v>
-      </c>
-      <c r="B47" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" t="s">
-        <v>121</v>
-      </c>
-      <c r="D47" t="s">
-        <v>157</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>62</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920226</v>
-      </c>
-      <c r="B48" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" t="s">
-        <v>158</v>
-      </c>
-      <c r="E48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>21330051920226</v>
-      </c>
-      <c r="B49" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" t="s">
-        <v>122</v>
-      </c>
-      <c r="D49" t="s">
-        <v>158</v>
-      </c>
-      <c r="E49" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" t="s">
-        <v>62</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>21330051920224</v>
-      </c>
-      <c r="B50" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" t="s">
-        <v>5</v>
-      </c>
-      <c r="F50" t="s">
-        <v>62</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>21330051920224</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" t="s">
-        <v>159</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>62</v>
-      </c>
-      <c r="G51">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="162">
   <si>
     <t>Materia</t>
   </si>
@@ -990,7 +990,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -1044,7 +1044,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -1067,7 +1067,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>9</v>
@@ -1121,7 +1121,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1144,7 +1144,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -1198,7 +1198,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1221,7 +1221,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1275,7 +1275,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1298,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -1352,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1375,7 +1375,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -1429,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1452,7 +1452,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -1506,7 +1506,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1529,7 +1529,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1583,7 +1583,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1606,7 +1606,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>8</v>
@@ -1660,7 +1660,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1683,7 +1683,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1737,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1760,7 +1760,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1814,7 +1814,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1837,7 +1837,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -1891,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1914,7 +1914,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C16">
         <v>9</v>
@@ -1968,7 +1968,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1991,7 +1991,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -2045,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2068,7 +2068,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -2122,7 +2122,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2145,7 +2145,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C19">
         <v>6</v>
@@ -2199,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2222,7 +2222,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -2276,7 +2276,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2299,7 +2299,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -2353,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2376,7 +2376,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -2430,7 +2430,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2453,7 +2453,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -2507,7 +2507,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2530,7 +2530,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2607,7 +2607,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C25">
         <v>9</v>
@@ -2661,7 +2661,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>9</v>
@@ -2684,7 +2684,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -2738,7 +2738,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2761,7 +2761,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -2815,7 +2815,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2838,7 +2838,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -2892,7 +2892,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -2915,7 +2915,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -2969,7 +2969,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -2992,7 +2992,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -3046,7 +3046,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -3069,7 +3069,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -3123,7 +3123,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -3146,7 +3146,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C32">
         <v>8</v>
@@ -3200,7 +3200,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>8</v>
@@ -3223,7 +3223,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>10</v>
@@ -3277,7 +3277,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3300,7 +3300,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C34">
         <v>7</v>
@@ -3354,7 +3354,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3377,7 +3377,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -3431,7 +3431,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3454,7 +3454,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C36">
         <v>7</v>
@@ -3508,7 +3508,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
         <v>7</v>
@@ -3531,7 +3531,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C37">
         <v>7</v>
@@ -3585,7 +3585,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -3608,7 +3608,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C38">
         <v>10</v>
@@ -3662,7 +3662,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U38">
         <v>10</v>
@@ -3685,7 +3685,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C39">
         <v>7</v>
@@ -3739,7 +3739,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -3762,7 +3762,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -3816,7 +3816,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>7</v>
@@ -3839,7 +3839,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -3893,7 +3893,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>7</v>
@@ -4026,7 +4026,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -4085,7 +4085,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>95</v>
@@ -4144,7 +4144,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -4203,7 +4203,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>95</v>
@@ -4262,7 +4262,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -4321,7 +4321,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>90</v>
@@ -4380,7 +4380,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -4439,7 +4439,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>95</v>
@@ -4498,7 +4498,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>95</v>
@@ -4557,7 +4557,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4616,7 +4616,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>95</v>
@@ -4675,7 +4675,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>85</v>
@@ -4734,7 +4734,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -4793,7 +4793,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>85</v>
@@ -4852,7 +4852,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>80</v>
@@ -4911,7 +4911,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>85</v>
@@ -4970,7 +4970,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -5029,7 +5029,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>60</v>
@@ -5088,7 +5088,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -5147,7 +5147,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>50</v>
@@ -5206,7 +5206,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>85</v>
@@ -5265,7 +5265,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -5324,7 +5324,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5383,7 +5383,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="C27">
         <v>45</v>
@@ -5442,7 +5442,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5501,7 +5501,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5560,7 +5560,7 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>90</v>
@@ -5619,7 +5619,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C31">
         <v>90</v>
@@ -5678,7 +5678,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -5737,7 +5737,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C33">
         <v>95</v>
@@ -5796,7 +5796,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -5855,7 +5855,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -5914,7 +5914,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C36">
         <v>85</v>
@@ -5973,7 +5973,7 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C37">
         <v>95</v>
@@ -6032,7 +6032,7 @@
         <v>46</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>100</v>
@@ -6091,7 +6091,7 @@
         <v>47</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C39">
         <v>100</v>
@@ -6150,7 +6150,7 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C40">
         <v>95</v>
@@ -6209,7 +6209,7 @@
         <v>49</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C41">
         <v>90</v>
@@ -6315,7 +6315,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6324,27 +6324,30 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>26.32</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
       </c>
       <c r="I2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -6353,19 +6356,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="G3">
-        <v>26.32</v>
+        <v>21.05</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6376,7 +6379,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -6385,19 +6388,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>78.95</v>
+        <v>81.58</v>
       </c>
       <c r="G4">
-        <v>21.05</v>
+        <v>18.42</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6408,7 +6411,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -6417,19 +6420,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>81.58</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="G5">
-        <v>18.42</v>
+        <v>15.79</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6440,7 +6443,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
@@ -6449,19 +6452,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>84.20999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="G6">
-        <v>15.79</v>
+        <v>7.89</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6472,7 +6475,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -6481,19 +6484,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>92.11</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G7">
-        <v>7.89</v>
+        <v>5.26</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6509,7 +6512,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6534,766 +6537,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920215</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920216</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920033</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920217</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920218</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920219</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920220</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920221</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920230</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920231</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920232</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920233</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920042</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920044</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920234</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920235</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920236</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" t="s">
-        <v>140</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920359</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920237</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" t="s">
-        <v>142</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920239</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920240</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920049</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920241</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920242</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920244</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920246</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920247</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920248</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" t="s">
-        <v>151</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920249</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920250</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920229</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" t="s">
-        <v>154</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920228</v>
-      </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" t="s">
-        <v>155</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920066</v>
-      </c>
-      <c r="B34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" t="s">
-        <v>156</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920227</v>
-      </c>
-      <c r="B35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" t="s">
-        <v>157</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920226</v>
-      </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" t="s">
-        <v>158</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920224</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920223</v>
-      </c>
-      <c r="B38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" t="s">
-        <v>123</v>
-      </c>
-      <c r="D38" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920222</v>
-      </c>
-      <c r="B39" t="s">
-        <v>100</v>
-      </c>
-      <c r="C39" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" t="s">
-        <v>161</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -7341,7 +6584,7 @@
         <v>124</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7358,7 +6601,7 @@
         <v>125</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7375,7 +6618,7 @@
         <v>126</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7392,7 +6635,7 @@
         <v>127</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7409,7 +6652,7 @@
         <v>128</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7426,7 +6669,7 @@
         <v>129</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7443,7 +6686,7 @@
         <v>130</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7460,7 +6703,7 @@
         <v>131</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7477,7 +6720,7 @@
         <v>132</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7494,7 +6737,7 @@
         <v>133</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7511,7 +6754,7 @@
         <v>134</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7528,7 +6771,7 @@
         <v>135</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7545,7 +6788,7 @@
         <v>136</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7562,7 +6805,7 @@
         <v>137</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7579,7 +6822,7 @@
         <v>138</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7596,7 +6839,7 @@
         <v>139</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7613,7 +6856,7 @@
         <v>140</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7630,7 +6873,7 @@
         <v>141</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7647,7 +6890,7 @@
         <v>142</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7664,7 +6907,7 @@
         <v>143</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7681,7 +6924,7 @@
         <v>144</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7698,7 +6941,7 @@
         <v>145</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7715,7 +6958,7 @@
         <v>146</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7732,7 +6975,7 @@
         <v>147</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7749,7 +6992,7 @@
         <v>148</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7766,7 +7009,7 @@
         <v>149</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7783,7 +7026,7 @@
         <v>150</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7800,7 +7043,7 @@
         <v>151</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7817,7 +7060,7 @@
         <v>152</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7834,7 +7077,7 @@
         <v>153</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7851,7 +7094,7 @@
         <v>154</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -7868,7 +7111,7 @@
         <v>155</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -7885,7 +7128,7 @@
         <v>156</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -7902,7 +7145,7 @@
         <v>157</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -7919,7 +7162,7 @@
         <v>158</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -7936,7 +7179,7 @@
         <v>159</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -7953,7 +7196,7 @@
         <v>160</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -7970,7 +7213,7 @@
         <v>161</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7980,7 +7223,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8024,27 +7267,27 @@
         <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920218</v>
+        <v>21330051920219</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -8058,39 +7301,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920219</v>
+        <v>21330051920044</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920219</v>
+        <v>21330051920239</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -8104,761 +7347,48 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920044</v>
+        <v>21330051920249</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920044</v>
+        <v>21330051920223</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920239</v>
-      </c>
-      <c r="B8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920239</v>
-      </c>
-      <c r="B9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>143</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920249</v>
-      </c>
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920249</v>
-      </c>
-      <c r="B11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920223</v>
-      </c>
-      <c r="B12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" t="s">
-        <v>160</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920223</v>
-      </c>
-      <c r="B13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920215</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920216</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920033</v>
-      </c>
-      <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920217</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920220</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920221</v>
-      </c>
-      <c r="B19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920230</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920231</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>133</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920232</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920233</v>
-      </c>
-      <c r="B23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920042</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920236</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>113</v>
-      </c>
-      <c r="D25" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920049</v>
-      </c>
-      <c r="B26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920241</v>
-      </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>146</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920244</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" t="s">
-        <v>148</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920246</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920247</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920248</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" t="s">
-        <v>151</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920250</v>
-      </c>
-      <c r="B32" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>119</v>
-      </c>
-      <c r="D32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920229</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" t="s">
-        <v>154</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920228</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" t="s">
-        <v>120</v>
-      </c>
-      <c r="D34" t="s">
-        <v>155</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920066</v>
-      </c>
-      <c r="B35" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" t="s">
-        <v>81</v>
-      </c>
-      <c r="D35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>62</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920227</v>
-      </c>
-      <c r="B36" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" t="s">
-        <v>121</v>
-      </c>
-      <c r="D36" t="s">
-        <v>157</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920226</v>
-      </c>
-      <c r="B37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" t="s">
-        <v>158</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>62</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920224</v>
-      </c>
-      <c r="B38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D38" t="s">
-        <v>159</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="167">
   <si>
     <t>Materia</t>
   </si>
@@ -207,7 +207,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Barañon Samaniego Graciela de los Ángeles</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>NC</t>
@@ -6350,7 +6365,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>38</v>
@@ -6382,7 +6397,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>38</v>
@@ -6414,7 +6429,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>38</v>
@@ -6446,7 +6461,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C6">
         <v>38</v>
@@ -6478,7 +6493,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C7">
         <v>38</v>
@@ -6521,16 +6536,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6555,16 +6570,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>60</v>
@@ -6575,13 +6590,13 @@
         <v>21330051920215</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6592,13 +6607,13 @@
         <v>21330051920216</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6609,13 +6624,13 @@
         <v>21330051920033</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6626,13 +6641,13 @@
         <v>21330051920217</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6643,13 +6658,13 @@
         <v>21330051920218</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6660,13 +6675,13 @@
         <v>21330051920219</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6677,13 +6692,13 @@
         <v>21330051920220</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6694,13 +6709,13 @@
         <v>21330051920221</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6711,13 +6726,13 @@
         <v>21330051920230</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6728,13 +6743,13 @@
         <v>21330051920231</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6745,13 +6760,13 @@
         <v>21330051920232</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6762,13 +6777,13 @@
         <v>21330051920233</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6779,13 +6794,13 @@
         <v>21330051920042</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6796,13 +6811,13 @@
         <v>21330051920044</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6813,13 +6828,13 @@
         <v>21330051920234</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6830,13 +6845,13 @@
         <v>21330051920235</v>
       </c>
       <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" t="s">
         <v>79</v>
       </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6847,13 +6862,13 @@
         <v>21330051920236</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6864,13 +6879,13 @@
         <v>21330051920359</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6881,13 +6896,13 @@
         <v>21330051920237</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6898,13 +6913,13 @@
         <v>21330051920239</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6915,13 +6930,13 @@
         <v>21330051920240</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6932,13 +6947,13 @@
         <v>21330051920049</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6949,13 +6964,13 @@
         <v>21330051920241</v>
       </c>
       <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
         <v>86</v>
       </c>
-      <c r="C24" t="s">
-        <v>81</v>
-      </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6966,13 +6981,13 @@
         <v>21330051920242</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6983,13 +6998,13 @@
         <v>21330051920244</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -7000,13 +7015,13 @@
         <v>21330051920246</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -7017,13 +7032,13 @@
         <v>21330051920247</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7034,13 +7049,13 @@
         <v>21330051920248</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7051,13 +7066,13 @@
         <v>21330051920249</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7068,13 +7083,13 @@
         <v>21330051920250</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -7085,13 +7100,13 @@
         <v>21330051920229</v>
       </c>
       <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
         <v>93</v>
       </c>
-      <c r="C32" t="s">
-        <v>88</v>
-      </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7102,13 +7117,13 @@
         <v>21330051920228</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7119,13 +7134,13 @@
         <v>21330051920066</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7136,13 +7151,13 @@
         <v>21330051920227</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7153,13 +7168,13 @@
         <v>21330051920226</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7170,13 +7185,13 @@
         <v>21330051920224</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D37" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -7187,13 +7202,13 @@
         <v>21330051920223</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7204,13 +7219,13 @@
         <v>21330051920222</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7232,16 +7247,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7258,13 +7273,13 @@
         <v>21330051920218</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -7281,13 +7296,13 @@
         <v>21330051920219</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -7304,19 +7319,19 @@
         <v>21330051920044</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7327,13 +7342,13 @@
         <v>21330051920239</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -7350,13 +7365,13 @@
         <v>21330051920249</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -7373,13 +7388,13 @@
         <v>21330051920223</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -213,12 +212,12 @@
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
+    <t>Barañon Samaniego Graciela de los Ángeles</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Barañon Samaniego Graciela de los Ángeles</t>
-  </si>
-  <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
@@ -237,295 +236,49 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AHUET</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DURAND</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>LOMAN</t>
+    <t>MADRIGAL</t>
+  </si>
+  <si>
+    <t>TEHUINTLE</t>
+  </si>
+  <si>
+    <t>ZACAMECAHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>MATLATECATL</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ZACAMECAHUA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>GRANADOS</t>
-  </si>
-  <si>
-    <t>DE GANTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>TZANAHUA</t>
   </si>
   <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>LETICIA ANETTE</t>
-  </si>
-  <si>
-    <t>ERANDI</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>PAZ AIDE</t>
-  </si>
-  <si>
-    <t>YARETZI VALERIA</t>
-  </si>
-  <si>
-    <t>JESUS MANUEL</t>
-  </si>
-  <si>
-    <t>LAURA EVELYN</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>ALONDRA VANNESSA</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>NOHEMI</t>
-  </si>
-  <si>
     <t>ARANZA DANAE</t>
   </si>
   <si>
-    <t>LORENA</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>DIEGO ANTONIO</t>
-  </si>
-  <si>
     <t>AMERICA PAOLA</t>
   </si>
   <si>
-    <t>DULCE DANIELA</t>
-  </si>
-  <si>
-    <t>AMY</t>
-  </si>
-  <si>
-    <t>MARIA DEL PILAR</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>CITLALI</t>
-  </si>
-  <si>
-    <t>ALMA PATRICIA</t>
-  </si>
-  <si>
     <t>LUCERO</t>
   </si>
   <si>
-    <t>GETSEMANI GUADALUPE</t>
-  </si>
-  <si>
-    <t>NESTOR JOSUE</t>
-  </si>
-  <si>
-    <t>DIANA GUADALUPE</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>JARITZA</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>MARIELA</t>
-  </si>
-  <si>
     <t>HARUMI</t>
-  </si>
-  <si>
-    <t>YAEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -578,11 +331,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1026,19 +780,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1065,16 +819,16 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1103,19 +857,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1139,13 +893,13 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1180,19 +934,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1216,19 +970,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1257,19 +1011,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1293,10 +1047,10 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1305,7 +1059,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1334,19 +1088,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1370,13 +1124,13 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1411,19 +1165,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1450,16 +1204,16 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1488,19 +1242,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1527,16 +1281,16 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1565,19 +1319,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1604,7 +1358,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1613,7 +1367,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1642,19 +1396,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1684,7 +1438,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1719,19 +1473,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1755,19 +1509,19 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>10</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1796,19 +1550,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1838,7 +1592,7 @@
         <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1873,19 +1627,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1912,16 +1666,16 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1950,19 +1704,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1992,7 +1746,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2027,19 +1781,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2066,7 +1820,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2104,19 +1858,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2140,7 +1894,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2181,19 +1935,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2258,19 +2012,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2300,13 +2054,13 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>6</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2335,19 +2089,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2412,19 +2166,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2454,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2489,19 +2243,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2566,19 +2320,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2602,7 +2356,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>5</v>
@@ -2643,19 +2397,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2685,7 +2439,7 @@
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2720,19 +2474,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2762,13 +2516,13 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2797,19 +2551,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2874,19 +2628,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2910,19 +2664,19 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2951,19 +2705,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2987,7 +2741,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -3028,19 +2782,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3067,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3076,7 +2830,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3105,19 +2859,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3141,13 +2895,13 @@
         <v>9</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>6</v>
@@ -3182,19 +2936,19 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3218,19 +2972,19 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3259,19 +3013,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3301,7 +3055,7 @@
         <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3336,19 +3090,19 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3375,16 +3129,16 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3413,19 +3167,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3449,19 +3203,19 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>6</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3490,19 +3244,19 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3526,13 +3280,13 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -3567,19 +3321,19 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3606,7 +3360,7 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3644,19 +3398,19 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3686,7 +3440,7 @@
         <v>10</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3721,19 +3475,19 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3757,13 +3511,13 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>9</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -3798,19 +3552,19 @@
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3837,7 +3591,7 @@
         <v>7</v>
       </c>
       <c r="V40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W40">
         <v>8</v>
@@ -3875,19 +3629,19 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>-1</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3911,10 +3665,10 @@
         <v>9</v>
       </c>
       <c r="U41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W41">
         <v>5</v>
@@ -4062,19 +3816,19 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -4121,19 +3875,19 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -4180,19 +3934,19 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4239,19 +3993,19 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4298,19 +4052,19 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4357,19 +4111,19 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4416,19 +4170,19 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4475,19 +4229,19 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4534,19 +4288,19 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4593,19 +4347,19 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4652,19 +4406,19 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4711,19 +4465,19 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4770,19 +4524,19 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4829,19 +4583,19 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4888,19 +4642,19 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4947,19 +4701,19 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -5006,19 +4760,19 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -5071,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5124,19 +4878,19 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5189,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -5242,19 +4996,19 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5301,19 +5055,19 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5360,19 +5114,19 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5478,19 +5232,19 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5537,19 +5291,19 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5596,19 +5350,19 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5655,19 +5409,19 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5714,19 +5468,19 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5773,19 +5527,19 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5832,19 +5586,19 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5891,19 +5645,19 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5950,19 +5704,19 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -6009,19 +5763,19 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -6068,19 +5822,19 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -6127,19 +5881,19 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -6186,19 +5940,19 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -6245,19 +5999,19 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -6294,6 +6048,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6339,24 +6095,24 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="G2">
-        <v>26.32</v>
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>21.1</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6376,25 +6132,25 @@
       <c r="E3">
         <v>8</v>
       </c>
-      <c r="F3">
-        <v>78.95</v>
-      </c>
-      <c r="G3">
-        <v>21.05</v>
+      <c r="F3" s="2">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="G3" s="2">
+        <v>21.1</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6408,25 +6164,25 @@
       <c r="E4">
         <v>7</v>
       </c>
-      <c r="F4">
-        <v>81.58</v>
-      </c>
-      <c r="G4">
-        <v>18.42</v>
+      <c r="F4" s="2">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="G4" s="2">
+        <v>18.4</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6435,24 +6191,24 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="G5">
-        <v>15.79</v>
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="G5" s="2">
+        <v>18.4</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6467,16 +6223,16 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>92.11</v>
-      </c>
-      <c r="G6">
-        <v>7.89</v>
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>86.8</v>
+      </c>
+      <c r="G6" s="2">
+        <v>13.2</v>
       </c>
       <c r="H6">
         <v>7.3</v>
@@ -6484,7 +6240,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6504,11 +6260,11 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="G7">
-        <v>5.26</v>
+      <c r="F7" s="2">
+        <v>94.7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5.3</v>
       </c>
       <c r="H7">
         <v>9.199999999999999</v>
@@ -6516,7 +6272,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6561,684 +6317,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21330051920215</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>21330051920216</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>21330051920033</v>
-      </c>
-      <c r="B4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>21330051920217</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>21330051920218</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>21330051920219</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>21330051920220</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>21330051920221</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>21330051920230</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>21330051920231</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>21330051920232</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>21330051920233</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>21330051920042</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>21330051920044</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>21330051920234</v>
-      </c>
-      <c r="B16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>21330051920235</v>
-      </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>21330051920236</v>
-      </c>
-      <c r="B18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>21330051920359</v>
-      </c>
-      <c r="B19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>21330051920237</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>21330051920239</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>148</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>21330051920240</v>
-      </c>
-      <c r="B22" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>21330051920049</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>87</v>
-      </c>
-      <c r="D23" t="s">
-        <v>150</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>21330051920241</v>
-      </c>
-      <c r="B24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" t="s">
-        <v>86</v>
-      </c>
-      <c r="D24" t="s">
-        <v>151</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>21330051920242</v>
-      </c>
-      <c r="B25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" t="s">
-        <v>152</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>21330051920244</v>
-      </c>
-      <c r="B26" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>21330051920246</v>
-      </c>
-      <c r="B27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>21330051920247</v>
-      </c>
-      <c r="B28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" t="s">
-        <v>121</v>
-      </c>
-      <c r="D28" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>21330051920248</v>
-      </c>
-      <c r="B29" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>21330051920249</v>
-      </c>
-      <c r="B30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" t="s">
-        <v>157</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>21330051920250</v>
-      </c>
-      <c r="B31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" t="s">
-        <v>158</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>21330051920229</v>
-      </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" t="s">
-        <v>159</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>21330051920228</v>
-      </c>
-      <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>21330051920066</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>21330051920227</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>21330051920226</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" t="s">
-        <v>127</v>
-      </c>
-      <c r="D36" t="s">
-        <v>163</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>21330051920224</v>
-      </c>
-      <c r="B37" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>21330051920223</v>
-      </c>
-      <c r="B38" t="s">
-        <v>104</v>
-      </c>
-      <c r="C38" t="s">
-        <v>128</v>
-      </c>
-      <c r="D38" t="s">
-        <v>165</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>21330051920222</v>
-      </c>
-      <c r="B39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7270,22 +6349,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920218</v>
+        <v>21330051920044</v>
       </c>
       <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>108</v>
-      </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7293,16 +6372,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920219</v>
+        <v>21330051920239</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -7316,22 +6395,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920044</v>
+        <v>21330051920249</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7339,16 +6418,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920239</v>
+        <v>21330051920223</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -7357,52 +6436,6 @@
         <v>62</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920249</v>
-      </c>
-      <c r="B6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920223</v>
-      </c>
-      <c r="B7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -789,7 +789,7 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -866,7 +866,7 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -902,7 +902,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -943,7 +943,7 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -979,7 +979,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1020,7 +1020,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1056,7 +1056,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1133,7 +1133,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1174,7 +1174,7 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1210,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1251,7 +1251,7 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -1287,7 +1287,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1328,7 +1328,7 @@
         <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1405,7 +1405,7 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1482,7 +1482,7 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1595,7 +1595,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1636,7 +1636,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>5</v>
@@ -1672,7 +1672,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1713,7 +1713,7 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>9</v>
@@ -1749,7 +1749,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1790,7 +1790,7 @@
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -1826,7 +1826,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -1867,7 +1867,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -1944,7 +1944,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -2021,7 +2021,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>9</v>
@@ -2057,7 +2057,7 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2098,7 +2098,7 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -2175,7 +2175,7 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>6</v>
@@ -2211,7 +2211,7 @@
         <v>10</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2252,7 +2252,7 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -2329,7 +2329,7 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>6</v>
@@ -2406,7 +2406,7 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -2442,7 +2442,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2483,7 +2483,7 @@
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2560,7 +2560,7 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2637,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>7</v>
@@ -2673,7 +2673,7 @@
         <v>9</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2714,7 +2714,7 @@
         <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>6</v>
@@ -2750,7 +2750,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2791,7 +2791,7 @@
         <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -2827,7 +2827,7 @@
         <v>8</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -2868,7 +2868,7 @@
         <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>6</v>
@@ -2904,7 +2904,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -2945,7 +2945,7 @@
         <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
         <v>8</v>
@@ -2981,7 +2981,7 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3022,7 +3022,7 @@
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
@@ -3099,7 +3099,7 @@
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3135,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3176,7 +3176,7 @@
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3212,7 +3212,7 @@
         <v>9</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3253,7 +3253,7 @@
         <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -3289,7 +3289,7 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3330,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M37">
         <v>6</v>
@@ -3366,7 +3366,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3407,7 +3407,7 @@
         <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>9</v>
@@ -3484,7 +3484,7 @@
         <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
         <v>7</v>
@@ -3520,7 +3520,7 @@
         <v>10</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -3561,7 +3561,7 @@
         <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
         <v>6</v>
@@ -3597,7 +3597,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3638,7 +3638,7 @@
         <v>6</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>6</v>
@@ -3825,7 +3825,7 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>106.7</v>
@@ -3884,7 +3884,7 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>106.7</v>
@@ -3943,7 +3943,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
         <v>106.7</v>
@@ -4002,7 +4002,7 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>106.7</v>
@@ -4061,7 +4061,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>106.7</v>
@@ -4120,7 +4120,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>106.7</v>
@@ -4179,7 +4179,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>106.7</v>
@@ -4238,7 +4238,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>106.7</v>
@@ -4297,7 +4297,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>106.7</v>
@@ -4356,7 +4356,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>106.7</v>
@@ -4415,7 +4415,7 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>106.7</v>
@@ -4474,7 +4474,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>106.7</v>
@@ -4533,7 +4533,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>106.7</v>
@@ -4592,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>106.7</v>
@@ -4710,7 +4710,7 @@
         <v>90</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>106.7</v>
@@ -4769,7 +4769,7 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>106.7</v>
@@ -4887,7 +4887,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>106.7</v>
@@ -5064,7 +5064,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>106.7</v>
@@ -5123,7 +5123,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>106.7</v>
@@ -5241,7 +5241,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>106.7</v>
@@ -5300,7 +5300,7 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>106.7</v>
@@ -5359,7 +5359,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
         <v>106.7</v>
@@ -5418,7 +5418,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
         <v>106.7</v>
@@ -5477,7 +5477,7 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>106.7</v>
@@ -5536,7 +5536,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>106.7</v>
@@ -5595,7 +5595,7 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>106.7</v>
@@ -5654,7 +5654,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>106.7</v>
@@ -5713,7 +5713,7 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>106.7</v>
@@ -5772,7 +5772,7 @@
         <v>100</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37">
         <v>106.7</v>
@@ -5831,7 +5831,7 @@
         <v>100</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38">
         <v>106.7</v>
@@ -5890,7 +5890,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39">
         <v>106.7</v>
@@ -5949,7 +5949,7 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M40">
         <v>106.7</v>
@@ -6008,7 +6008,7 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M41">
         <v>106.7</v>
@@ -6203,7 +6203,7 @@
         <v>18.4</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -777,7 +777,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -854,7 +854,7 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -931,7 +931,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -1008,7 +1008,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1085,7 +1085,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -1121,7 +1121,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1162,7 +1162,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1239,7 +1239,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -1393,7 +1393,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>8</v>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -1547,7 +1547,7 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>7</v>
@@ -1624,7 +1624,7 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>7</v>
@@ -1701,7 +1701,7 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -1855,7 +1855,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -1891,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -1932,7 +1932,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>6</v>
@@ -2009,7 +2009,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -2086,7 +2086,7 @@
         <v>5</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2122,7 +2122,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>6</v>
@@ -2240,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>5</v>
@@ -2317,7 +2317,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>5</v>
@@ -2353,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2394,7 +2394,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2471,7 +2471,7 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -2548,7 +2548,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -2625,7 +2625,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>8</v>
@@ -2661,7 +2661,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2702,7 +2702,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>8</v>
@@ -2779,7 +2779,7 @@
         <v>6</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -2856,7 +2856,7 @@
         <v>5</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>5</v>
@@ -2892,7 +2892,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -2933,7 +2933,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -3010,7 +3010,7 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3087,7 +3087,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>6</v>
@@ -3164,7 +3164,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>10</v>
@@ -3241,7 +3241,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>5</v>
@@ -3318,7 +3318,7 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>6</v>
@@ -3354,7 +3354,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -3395,7 +3395,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>10</v>
@@ -3472,7 +3472,7 @@
         <v>7</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
         <v>8</v>
@@ -3549,7 +3549,7 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I40">
         <v>7</v>
@@ -3626,7 +3626,7 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>5</v>
@@ -3813,7 +3813,7 @@
         <v>106.7</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3872,7 +3872,7 @@
         <v>106.7</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -3931,7 +3931,7 @@
         <v>106.7</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -3990,7 +3990,7 @@
         <v>106.7</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -4049,7 +4049,7 @@
         <v>106.7</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>95</v>
@@ -4108,7 +4108,7 @@
         <v>106.7</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -4167,7 +4167,7 @@
         <v>106.7</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>90</v>
@@ -4226,7 +4226,7 @@
         <v>106.7</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>95</v>
@@ -4285,7 +4285,7 @@
         <v>106.7</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -4344,7 +4344,7 @@
         <v>106.7</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>95</v>
@@ -4403,7 +4403,7 @@
         <v>106.7</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4462,7 +4462,7 @@
         <v>106.7</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>80</v>
@@ -4521,7 +4521,7 @@
         <v>106.7</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16">
         <v>95</v>
@@ -4698,7 +4698,7 @@
         <v>106.7</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="I19">
         <v>80</v>
@@ -4757,7 +4757,7 @@
         <v>106.7</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -4816,7 +4816,7 @@
         <v>86.7</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>106.7</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -4934,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>106.7</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -5111,7 +5111,7 @@
         <v>106.7</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -5229,7 +5229,7 @@
         <v>106.7</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>95</v>
@@ -5288,7 +5288,7 @@
         <v>106.7</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -5347,7 +5347,7 @@
         <v>106.7</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>95</v>
@@ -5406,7 +5406,7 @@
         <v>106.7</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>90</v>
@@ -5465,7 +5465,7 @@
         <v>106.7</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -5524,7 +5524,7 @@
         <v>106.7</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33">
         <v>100</v>
@@ -5583,7 +5583,7 @@
         <v>106.7</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34">
         <v>100</v>
@@ -5642,7 +5642,7 @@
         <v>106.7</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35">
         <v>100</v>
@@ -5701,7 +5701,7 @@
         <v>106.7</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36">
         <v>90</v>
@@ -5760,7 +5760,7 @@
         <v>106.7</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37">
         <v>100</v>
@@ -5819,7 +5819,7 @@
         <v>106.7</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38">
         <v>100</v>
@@ -5878,7 +5878,7 @@
         <v>106.7</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I39">
         <v>100</v>
@@ -5937,7 +5937,7 @@
         <v>106.7</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I40">
         <v>85</v>
@@ -5996,7 +5996,7 @@
         <v>106.7</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I41">
         <v>95</v>
@@ -6255,16 +6255,16 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>94.7</v>
+        <v>89.5</v>
       </c>
       <c r="G7" s="2">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="H7">
         <v>9.199999999999999</v>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -1778,7 +1778,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -1814,7 +1814,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -4580,7 +4580,7 @@
         <v>80</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>95</v>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -3810,7 +3810,7 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -3819,7 +3819,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -3828,25 +3828,25 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3869,16 +3869,16 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J5">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -3887,25 +3887,25 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3928,7 +3928,7 @@
         <v>100</v>
       </c>
       <c r="G6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>100</v>
@@ -3937,7 +3937,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3946,25 +3946,25 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3987,13 +3987,13 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J7">
         <v>95</v>
@@ -4005,25 +4005,25 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4046,16 +4046,16 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J8">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -4064,25 +4064,25 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4105,13 +4105,13 @@
         <v>100</v>
       </c>
       <c r="G9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J9">
         <v>95</v>
@@ -4123,25 +4123,25 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4164,7 +4164,7 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -4173,7 +4173,7 @@
         <v>90</v>
       </c>
       <c r="J10">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -4182,25 +4182,25 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4223,7 +4223,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -4232,7 +4232,7 @@
         <v>95</v>
       </c>
       <c r="J11">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -4241,25 +4241,25 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4282,13 +4282,13 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4300,25 +4300,25 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4341,16 +4341,16 @@
         <v>100</v>
       </c>
       <c r="G13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4359,25 +4359,25 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4400,16 +4400,16 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4418,25 +4418,25 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4459,16 +4459,16 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>100</v>
       </c>
       <c r="I15">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J15">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4477,25 +4477,25 @@
         <v>100</v>
       </c>
       <c r="M15">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4518,16 +4518,16 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H16">
         <v>100</v>
       </c>
       <c r="I16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J16">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -4536,25 +4536,25 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4577,43 +4577,43 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H17">
         <v>100</v>
       </c>
       <c r="I17">
+        <v>90</v>
+      </c>
+      <c r="J17">
+        <v>87.5</v>
+      </c>
+      <c r="K17">
         <v>95</v>
       </c>
-      <c r="J17">
-        <v>85</v>
-      </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>106.7</v>
+        <v>87.5</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4636,43 +4636,43 @@
         <v>75</v>
       </c>
       <c r="G18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I18">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J18">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K18">
         <v>90</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="M18">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4695,43 +4695,43 @@
         <v>100</v>
       </c>
       <c r="G19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I19">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K19">
         <v>90</v>
       </c>
       <c r="L19">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="M19">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4754,7 +4754,7 @@
         <v>100</v>
       </c>
       <c r="G20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H20">
         <v>100</v>
@@ -4763,7 +4763,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -4772,25 +4772,25 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4813,43 +4813,43 @@
         <v>75</v>
       </c>
       <c r="G21">
-        <v>86.7</v>
+        <v>81.3</v>
       </c>
       <c r="H21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K21">
         <v>90</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>40.6</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4872,7 +4872,7 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>100</v>
@@ -4890,25 +4890,25 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4934,37 +4934,37 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K23">
         <v>90</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -4990,43 +4990,43 @@
         <v>75</v>
       </c>
       <c r="G24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I24">
-        <v>50</v>
+        <v>67.5</v>
       </c>
       <c r="J24">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K24">
         <v>90</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="M24">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5049,7 +5049,7 @@
         <v>100</v>
       </c>
       <c r="G25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H25">
         <v>100</v>
@@ -5058,7 +5058,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -5067,25 +5067,25 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5108,7 +5108,7 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H26">
         <v>100</v>
@@ -5126,25 +5126,25 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5170,37 +5170,37 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -5226,16 +5226,16 @@
         <v>100</v>
       </c>
       <c r="G28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H28">
         <v>100</v>
       </c>
       <c r="I28">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J28">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -5244,25 +5244,25 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5285,7 +5285,7 @@
         <v>100</v>
       </c>
       <c r="G29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H29">
         <v>100</v>
@@ -5294,7 +5294,7 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -5303,25 +5303,25 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5344,16 +5344,16 @@
         <v>100</v>
       </c>
       <c r="G30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H30">
         <v>100</v>
       </c>
       <c r="I30">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J30">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -5362,25 +5362,25 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5403,7 +5403,7 @@
         <v>100</v>
       </c>
       <c r="G31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>100</v>
@@ -5421,25 +5421,25 @@
         <v>100</v>
       </c>
       <c r="M31">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5462,7 +5462,7 @@
         <v>100</v>
       </c>
       <c r="G32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H32">
         <v>100</v>
@@ -5471,7 +5471,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -5480,25 +5480,25 @@
         <v>100</v>
       </c>
       <c r="M32">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5521,16 +5521,16 @@
         <v>100</v>
       </c>
       <c r="G33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H33">
         <v>100</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J33">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -5539,25 +5539,25 @@
         <v>100</v>
       </c>
       <c r="M33">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5580,7 +5580,7 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H34">
         <v>100</v>
@@ -5598,25 +5598,25 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5639,7 +5639,7 @@
         <v>100</v>
       </c>
       <c r="G35">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H35">
         <v>100</v>
@@ -5657,25 +5657,25 @@
         <v>100</v>
       </c>
       <c r="M35">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5698,16 +5698,16 @@
         <v>100</v>
       </c>
       <c r="G36">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H36">
         <v>100</v>
       </c>
       <c r="I36">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="J36">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -5716,25 +5716,25 @@
         <v>100</v>
       </c>
       <c r="M36">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5757,16 +5757,16 @@
         <v>100</v>
       </c>
       <c r="G37">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H37">
         <v>100</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J37">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -5775,25 +5775,25 @@
         <v>100</v>
       </c>
       <c r="M37">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5816,7 +5816,7 @@
         <v>100</v>
       </c>
       <c r="G38">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H38">
         <v>100</v>
@@ -5834,25 +5834,25 @@
         <v>100</v>
       </c>
       <c r="M38">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5875,7 +5875,7 @@
         <v>100</v>
       </c>
       <c r="G39">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H39">
         <v>100</v>
@@ -5893,25 +5893,25 @@
         <v>100</v>
       </c>
       <c r="M39">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -5934,16 +5934,16 @@
         <v>100</v>
       </c>
       <c r="G40">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H40">
         <v>100</v>
       </c>
       <c r="I40">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J40">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -5952,25 +5952,25 @@
         <v>100</v>
       </c>
       <c r="M40">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -5993,43 +5993,43 @@
         <v>80</v>
       </c>
       <c r="G41">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="H41">
         <v>100</v>
       </c>
       <c r="I41">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="J41">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K41">
         <v>100</v>
       </c>
       <c r="L41">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M41">
-        <v>106.7</v>
+        <v>100</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -209,18 +209,18 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Barañon Samaniego Graciela de los Ángeles</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
-    <t>Barañon Samaniego Graciela de los Ángeles</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -236,7 +236,7 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>MADRIGAL</t>
@@ -248,7 +248,7 @@
     <t>ZACAMECAHUA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -260,7 +260,7 @@
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>ARANZA DANAE</t>
+    <t>LIZBETH JOSELYN</t>
   </si>
   <si>
     <t>AMERICA PAOLA</t>
@@ -804,10 +804,10 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -825,7 +825,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -881,10 +881,10 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -958,10 +958,10 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -979,7 +979,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1035,10 +1035,10 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1112,10 +1112,10 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1189,10 +1189,10 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1266,10 +1266,10 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1284,7 +1284,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>8</v>
@@ -1343,10 +1343,10 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1420,10 +1420,10 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1441,7 +1441,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1497,10 +1497,10 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1574,10 +1574,10 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1651,10 +1651,10 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1728,10 +1728,10 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1805,10 +1805,10 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1823,7 +1823,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -1882,10 +1882,10 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -1959,10 +1959,10 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -1977,7 +1977,7 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2036,10 +2036,10 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2054,7 +2054,7 @@
         <v>10</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2113,10 +2113,10 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2190,10 +2190,10 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2208,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2267,10 +2267,10 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2344,10 +2344,10 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2421,10 +2421,10 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2498,10 +2498,10 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2516,10 +2516,10 @@
         <v>10</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2575,10 +2575,10 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2652,10 +2652,10 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2729,10 +2729,10 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2750,7 +2750,7 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2806,10 +2806,10 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -2883,10 +2883,10 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -2960,10 +2960,10 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -2981,7 +2981,7 @@
         <v>10</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>9</v>
@@ -3037,10 +3037,10 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3114,10 +3114,10 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3135,7 +3135,7 @@
         <v>9</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3191,10 +3191,10 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3268,10 +3268,10 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3286,10 +3286,10 @@
         <v>8</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3345,10 +3345,10 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3366,7 +3366,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>6</v>
@@ -3422,10 +3422,10 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3499,10 +3499,10 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3576,10 +3576,10 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -3597,7 +3597,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -3653,10 +3653,10 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -3671,7 +3671,7 @@
         <v>5</v>
       </c>
       <c r="W41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>5</v>
@@ -3843,7 +3843,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3902,7 +3902,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4607,7 +4607,7 @@
         <v>87.5</v>
       </c>
       <c r="Q17">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4666,10 +4666,10 @@
         <v>65</v>
       </c>
       <c r="Q18">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="R18">
-        <v>37.5</v>
+        <v>23.4</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4725,10 +4725,10 @@
         <v>90</v>
       </c>
       <c r="Q19">
-        <v>90</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="R19">
-        <v>55</v>
+        <v>34.4</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -4843,10 +4843,10 @@
         <v>40</v>
       </c>
       <c r="Q21">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="R21">
-        <v>37.5</v>
+        <v>23.4</v>
       </c>
       <c r="S21">
         <v>40.6</v>
@@ -4961,10 +4961,10 @@
         <v>40</v>
       </c>
       <c r="Q23">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="R23">
-        <v>37.5</v>
+        <v>23.4</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -5020,10 +5020,10 @@
         <v>70</v>
       </c>
       <c r="Q24">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="R24">
-        <v>37.5</v>
+        <v>23.4</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5197,10 +5197,10 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>45</v>
+        <v>28.1</v>
       </c>
       <c r="R27">
-        <v>37.5</v>
+        <v>23.4</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6023,10 +6023,10 @@
         <v>90</v>
       </c>
       <c r="Q41">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R41">
-        <v>70</v>
+        <v>43.8</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -6118,7 +6118,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -6127,16 +6127,16 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>78.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>21.1</v>
+        <v>18.4</v>
       </c>
       <c r="H3">
         <v>8.199999999999999</v>
@@ -6150,7 +6150,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6171,7 +6171,7 @@
         <v>18.4</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6182,7 +6182,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6191,16 +6191,16 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>81.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="G5" s="2">
-        <v>18.4</v>
+        <v>13.2</v>
       </c>
       <c r="H5">
         <v>7.3</v>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -6235,7 +6235,7 @@
         <v>13.2</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6317,7 +6317,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920044</v>
+        <v>21330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
@@ -6361,7 +6361,7 @@
         <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920239</v>
+        <v>21330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6395,16 +6395,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920249</v>
+        <v>21330051920239</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -6418,16 +6418,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920223</v>
+        <v>21330051920249</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6436,6 +6436,29 @@
         <v>62</v>
       </c>
       <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920223</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -206,24 +206,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Barañon Samaniego Graciela de los Ángeles</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Barañon Samaniego Graciela de los Ángeles</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
+    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -239,10 +239,7 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>MADRIGAL</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
+    <t>ZEPEDA</t>
   </si>
   <si>
     <t>ZACAMECAHUA</t>
@@ -251,10 +248,7 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>DE LA LUZ</t>
@@ -263,10 +257,7 @@
     <t>LIZBETH JOSELYN</t>
   </si>
   <si>
-    <t>AMERICA PAOLA</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
+    <t>YAEL</t>
   </si>
   <si>
     <t>HARUMI</t>
@@ -795,13 +786,13 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -810,7 +801,7 @@
         <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -872,13 +863,13 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -887,7 +878,7 @@
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -949,13 +940,13 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -964,7 +955,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -982,7 +973,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1026,13 +1017,13 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>9</v>
@@ -1041,7 +1032,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1103,13 +1094,13 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1118,16 +1109,16 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>7</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1136,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1180,13 +1171,13 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>8</v>
@@ -1195,7 +1186,7 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1257,13 +1248,13 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -1272,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1290,7 +1281,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1334,13 +1325,13 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1349,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1411,13 +1402,13 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -1426,7 +1417,7 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1488,13 +1479,13 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1503,7 +1494,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1565,13 +1556,13 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1580,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1598,7 +1589,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1642,13 +1633,13 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -1657,7 +1648,7 @@
         <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1666,7 +1657,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1675,7 +1666,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1719,13 +1710,13 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -1734,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1796,13 +1787,13 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -1811,16 +1802,16 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>7</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -1873,13 +1864,13 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -1888,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -1950,13 +1941,13 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>7</v>
@@ -1965,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2027,13 +2018,13 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2042,7 +2033,7 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2060,7 +2051,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2104,13 +2095,13 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -2119,10 +2110,10 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2181,13 +2172,13 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -2196,7 +2187,7 @@
         <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2205,7 +2196,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2214,7 +2205,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2258,13 +2249,13 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>5</v>
@@ -2273,7 +2264,7 @@
         <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
         <v>5</v>
@@ -2335,13 +2326,13 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>5</v>
@@ -2350,7 +2341,7 @@
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2368,7 +2359,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2412,13 +2403,13 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2427,7 +2418,7 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2489,13 +2480,13 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>9</v>
@@ -2504,7 +2495,7 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2522,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2566,13 +2557,13 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>5</v>
@@ -2581,7 +2572,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2643,13 +2634,13 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>10</v>
@@ -2658,7 +2649,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2667,7 +2658,7 @@
         <v>7</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2720,13 +2711,13 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>8</v>
@@ -2735,7 +2726,7 @@
         <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2797,13 +2788,13 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>8</v>
@@ -2812,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2821,7 +2812,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2874,13 +2865,13 @@
         <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>8</v>
@@ -2889,10 +2880,10 @@
         <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -2907,7 +2898,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2951,13 +2942,13 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
         <v>10</v>
@@ -2966,7 +2957,7 @@
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3028,13 +3019,13 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3043,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3105,13 +3096,13 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3120,7 +3111,7 @@
         <v>6</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3138,7 +3129,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3182,13 +3173,13 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>10</v>
@@ -3197,7 +3188,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3259,13 +3250,13 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -3274,7 +3265,7 @@
         <v>7</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3283,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>9</v>
@@ -3336,13 +3327,13 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>9</v>
@@ -3351,7 +3342,7 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3369,7 +3360,7 @@
         <v>8</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3413,13 +3404,13 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>10</v>
@@ -3428,7 +3419,7 @@
         <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3490,13 +3481,13 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>10</v>
@@ -3505,7 +3496,7 @@
         <v>8</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3567,13 +3558,13 @@
         <v>6</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
         <v>9</v>
@@ -3582,7 +3573,7 @@
         <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3644,13 +3635,13 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -3659,7 +3650,7 @@
         <v>5</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -3677,7 +3668,7 @@
         <v>5</v>
       </c>
       <c r="Y41">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3837,7 +3828,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3896,7 +3887,7 @@
         <v>97.5</v>
       </c>
       <c r="P5">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3955,7 +3946,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4014,7 +4005,7 @@
         <v>97.5</v>
       </c>
       <c r="P7">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4073,7 +4064,7 @@
         <v>97.5</v>
       </c>
       <c r="P8">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4132,7 +4123,7 @@
         <v>95</v>
       </c>
       <c r="P9">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4191,7 +4182,7 @@
         <v>90</v>
       </c>
       <c r="P10">
-        <v>92.5</v>
+        <v>95.2</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4250,7 +4241,7 @@
         <v>95</v>
       </c>
       <c r="P11">
-        <v>90</v>
+        <v>93.5</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4368,7 +4359,7 @@
         <v>97.5</v>
       </c>
       <c r="P13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4427,7 +4418,7 @@
         <v>97.5</v>
       </c>
       <c r="P14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4486,7 +4477,7 @@
         <v>82.5</v>
       </c>
       <c r="P15">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4545,7 +4536,7 @@
         <v>97.5</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4604,7 +4595,7 @@
         <v>90</v>
       </c>
       <c r="P17">
-        <v>87.5</v>
+        <v>88.7</v>
       </c>
       <c r="Q17">
         <v>96.90000000000001</v>
@@ -4613,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4657,13 +4648,13 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="O18">
         <v>65</v>
       </c>
       <c r="P18">
-        <v>65</v>
+        <v>58.1</v>
       </c>
       <c r="Q18">
         <v>56.3</v>
@@ -4672,7 +4663,7 @@
         <v>23.4</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4716,13 +4707,13 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="O19">
         <v>82.5</v>
       </c>
       <c r="P19">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q19">
         <v>84.40000000000001</v>
@@ -4781,7 +4772,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4834,13 +4825,13 @@
         <v>40.6</v>
       </c>
       <c r="N21">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="O21">
         <v>30</v>
       </c>
       <c r="P21">
-        <v>40</v>
+        <v>25.8</v>
       </c>
       <c r="Q21">
         <v>56.3</v>
@@ -4849,7 +4840,7 @@
         <v>23.4</v>
       </c>
       <c r="S21">
-        <v>40.6</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4952,13 +4943,13 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="O23">
         <v>25</v>
       </c>
       <c r="P23">
-        <v>40</v>
+        <v>25.8</v>
       </c>
       <c r="Q23">
         <v>56.3</v>
@@ -5011,13 +5002,13 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="O24">
         <v>67.5</v>
       </c>
       <c r="P24">
-        <v>70</v>
+        <v>45.2</v>
       </c>
       <c r="Q24">
         <v>56.3</v>
@@ -5026,7 +5017,7 @@
         <v>23.4</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5076,7 +5067,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5188,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>21.4</v>
+        <v>13.4</v>
       </c>
       <c r="O27">
         <v>22.5</v>
@@ -5253,7 +5244,7 @@
         <v>97.5</v>
       </c>
       <c r="P28">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5312,7 +5303,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>95</v>
+        <v>96.8</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5371,7 +5362,7 @@
         <v>92.5</v>
       </c>
       <c r="P30">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5430,7 +5421,7 @@
         <v>90</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5489,7 +5480,7 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q32">
         <v>100</v>
@@ -5548,7 +5539,7 @@
         <v>97.5</v>
       </c>
       <c r="P33">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5607,7 +5598,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>85</v>
+        <v>88.7</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -5725,7 +5716,7 @@
         <v>87.5</v>
       </c>
       <c r="P36">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -5784,7 +5775,7 @@
         <v>97.5</v>
       </c>
       <c r="P37">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -5961,7 +5952,7 @@
         <v>90</v>
       </c>
       <c r="P40">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6020,7 +6011,7 @@
         <v>92.5</v>
       </c>
       <c r="P41">
-        <v>90</v>
+        <v>90.3</v>
       </c>
       <c r="Q41">
         <v>90.59999999999999</v>
@@ -6086,7 +6077,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6095,19 +6086,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>78.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>21.1</v>
+        <v>18.4</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6118,7 +6109,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -6139,7 +6130,7 @@
         <v>18.4</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6150,7 +6141,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6159,16 +6150,16 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>81.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="G4" s="2">
-        <v>18.4</v>
+        <v>13.2</v>
       </c>
       <c r="H4">
         <v>7.3</v>
@@ -6182,7 +6173,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -6203,7 +6194,7 @@
         <v>13.2</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6214,7 +6205,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -6235,7 +6226,7 @@
         <v>13.2</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6246,7 +6237,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -6255,19 +6246,19 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>89.5</v>
+        <v>86.8</v>
       </c>
       <c r="G7" s="2">
-        <v>10.5</v>
+        <v>13.2</v>
       </c>
       <c r="H7">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6355,16 +6346,16 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6378,16 +6369,16 @@
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6395,19 +6386,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920239</v>
+        <v>21330051920222</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
@@ -6418,22 +6409,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920249</v>
+        <v>21330051920222</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6444,19 +6435,19 @@
         <v>21330051920223</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G6">
         <v>5</v>

--- a/grupos/4ARHM - Estadisticos 20222.xlsx
+++ b/grupos/4ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="78">
   <si>
     <t>Materia</t>
   </si>
@@ -236,25 +236,16 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
     <t>ZACAMECAHUA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
   </si>
   <si>
     <t>YAEL</t>
@@ -789,7 +780,7 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>10</v>
@@ -866,7 +857,7 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -943,7 +934,7 @@
         <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>10</v>
@@ -961,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1020,7 +1011,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>10</v>
@@ -1097,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>5</v>
@@ -1174,7 +1165,7 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>10</v>
@@ -1192,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1251,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>9</v>
@@ -1269,7 +1260,7 @@
         <v>9</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1328,7 +1319,7 @@
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>10</v>
@@ -1405,7 +1396,7 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>8</v>
@@ -1423,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1482,7 +1473,7 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>10</v>
@@ -1559,7 +1550,7 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>10</v>
@@ -1577,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1636,7 +1627,7 @@
         <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>5</v>
@@ -1654,7 +1645,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -1713,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -1731,7 +1722,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1790,7 +1781,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>9</v>
@@ -1867,7 +1858,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -1944,7 +1935,7 @@
         <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>5</v>
@@ -1962,7 +1953,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2021,7 +2012,7 @@
         <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>10</v>
@@ -2098,7 +2089,7 @@
         <v>5</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>5</v>
@@ -2175,7 +2166,7 @@
         <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>10</v>
@@ -2193,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>9</v>
@@ -2252,7 +2243,7 @@
         <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>5</v>
@@ -2329,7 +2320,7 @@
         <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -2359,7 +2350,7 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2406,7 +2397,7 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
         <v>10</v>
@@ -2483,7 +2474,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>9</v>
@@ -2501,7 +2492,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2560,7 +2551,7 @@
         <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>5</v>
@@ -2637,7 +2628,7 @@
         <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -2714,7 +2705,7 @@
         <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>9</v>
@@ -2791,7 +2782,7 @@
         <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>10</v>
@@ -2868,7 +2859,7 @@
         <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>7</v>
@@ -2945,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>9</v>
@@ -3022,7 +3013,7 @@
         <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
         <v>10</v>
@@ -3099,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>9</v>
@@ -3117,7 +3108,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3176,7 +3167,7 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>10</v>
@@ -3253,7 +3244,7 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>10</v>
@@ -3330,7 +3321,7 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>10</v>
@@ -3407,7 +3398,7 @@
         <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
         <v>10</v>
@@ -3484,7 +3475,7 @@
         <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>10</v>
@@ -3561,7 +3552,7 @@
         <v>8</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
         <v>10</v>
@@ -3638,7 +3629,7 @@
         <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P41">
         <v>5</v>
@@ -3825,7 +3816,7 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P4">
         <v>91.90000000000001</v>
@@ -3884,7 +3875,7 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P5">
         <v>91.90000000000001</v>
@@ -4002,7 +3993,7 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P7">
         <v>96.8</v>
@@ -4061,7 +4052,7 @@
         <v>100</v>
       </c>
       <c r="O8">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="P8">
         <v>96.8</v>
@@ -4120,7 +4111,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P9">
         <v>96.8</v>
@@ -4179,7 +4170,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P10">
         <v>95.2</v>
@@ -4238,7 +4229,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P11">
         <v>93.5</v>
@@ -4297,7 +4288,7 @@
         <v>100</v>
       </c>
       <c r="O12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P12">
         <v>100</v>
@@ -4356,7 +4347,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P13">
         <v>98.40000000000001</v>
@@ -4415,7 +4406,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P14">
         <v>98.40000000000001</v>
@@ -4474,7 +4465,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>82.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P15">
         <v>90.3</v>
@@ -4533,7 +4524,7 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P16">
         <v>91.90000000000001</v>
@@ -4592,7 +4583,7 @@
         <v>100</v>
       </c>
       <c r="O17">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P17">
         <v>88.7</v>
@@ -4651,7 +4642,7 @@
         <v>31.3</v>
       </c>
       <c r="O18">
-        <v>65</v>
+        <v>40.6</v>
       </c>
       <c r="P18">
         <v>58.1</v>
@@ -4710,7 +4701,7 @@
         <v>95.5</v>
       </c>
       <c r="O19">
-        <v>82.5</v>
+        <v>79.7</v>
       </c>
       <c r="P19">
         <v>91.90000000000001</v>
@@ -4828,7 +4819,7 @@
         <v>56.3</v>
       </c>
       <c r="O21">
-        <v>30</v>
+        <v>18.8</v>
       </c>
       <c r="P21">
         <v>25.8</v>
@@ -4946,7 +4937,7 @@
         <v>56.3</v>
       </c>
       <c r="O23">
-        <v>25</v>
+        <v>15.6</v>
       </c>
       <c r="P23">
         <v>25.8</v>
@@ -5005,7 +4996,7 @@
         <v>31.3</v>
       </c>
       <c r="O24">
-        <v>67.5</v>
+        <v>42.2</v>
       </c>
       <c r="P24">
         <v>45.2</v>
@@ -5182,7 +5173,7 @@
         <v>13.4</v>
       </c>
       <c r="O27">
-        <v>22.5</v>
+        <v>14.1</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -5241,7 +5232,7 @@
         <v>100</v>
       </c>
       <c r="O28">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="P28">
         <v>90.3</v>
@@ -5300,7 +5291,7 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P29">
         <v>96.8</v>
@@ -5359,7 +5350,7 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="P30">
         <v>91.90000000000001</v>
@@ -5418,7 +5409,7 @@
         <v>100</v>
       </c>
       <c r="O31">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P31">
         <v>98.40000000000001</v>
@@ -5477,7 +5468,7 @@
         <v>100</v>
       </c>
       <c r="O32">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P32">
         <v>98.40000000000001</v>
@@ -5536,7 +5527,7 @@
         <v>100</v>
       </c>
       <c r="O33">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P33">
         <v>91.90000000000001</v>
@@ -5713,7 +5704,7 @@
         <v>100</v>
       </c>
       <c r="O36">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="P36">
         <v>91.90000000000001</v>
@@ -5772,7 +5763,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P37">
         <v>91.90000000000001</v>
@@ -5949,7 +5940,7 @@
         <v>100</v>
       </c>
       <c r="O40">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="P40">
         <v>91.90000000000001</v>
@@ -6008,7 +5999,7 @@
         <v>100</v>
       </c>
       <c r="O41">
-        <v>92.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P41">
         <v>90.3</v>
@@ -6150,19 +6141,19 @@
         <v>38</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>86.8</v>
+        <v>84.2</v>
       </c>
       <c r="G4" s="2">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6182,16 +6173,16 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>86.8</v>
+        <v>84.2</v>
       </c>
       <c r="G5" s="2">
-        <v>13.2</v>
+        <v>15.8</v>
       </c>
       <c r="H5">
         <v>7.7</v>
@@ -6308,7 +6299,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6340,16 +6331,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920235</v>
+        <v>21330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -6363,16 +6354,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920235</v>
+        <v>21330051920222</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -6386,70 +6377,24 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920222</v>
+        <v>21330051920223</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920222</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920223</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>
